--- a/research/traditional_assets/database/data/singapore/singapore_computers_peripherals.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_computers_peripherals.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="sgx_b69" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,118 +590,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.00025</v>
+        <v>-0.0258</v>
       </c>
       <c r="G2">
-        <v>0.0503531040849296</v>
+        <v>0.04022451317296679</v>
       </c>
       <c r="H2">
-        <v>0.01144703438726056</v>
+        <v>0.001901489117983965</v>
       </c>
       <c r="I2">
-        <v>-0.01181629356104316</v>
+        <v>-0.02109965635738831</v>
       </c>
       <c r="J2">
-        <v>-0.01146572289692844</v>
+        <v>-0.02056931364354044</v>
       </c>
       <c r="K2">
-        <v>3.952000000000001</v>
+        <v>-8.370000000000001</v>
       </c>
       <c r="L2">
-        <v>0.009120701592430188</v>
+        <v>-0.01917525773195877</v>
       </c>
       <c r="M2">
-        <v>2.3124</v>
+        <v>5.244</v>
       </c>
       <c r="N2">
-        <v>0.01039748201438849</v>
+        <v>0.03975739196360879</v>
       </c>
       <c r="O2">
-        <v>0.5851214574898784</v>
+        <v>-0.6265232974910393</v>
       </c>
       <c r="P2">
-        <v>1.8364</v>
+        <v>3.32</v>
       </c>
       <c r="Q2">
-        <v>0.008257194244604317</v>
+        <v>0.02517058377558756</v>
       </c>
       <c r="R2">
-        <v>0.4646761133603238</v>
+        <v>-0.3966547192353643</v>
       </c>
       <c r="S2">
-        <v>0.476</v>
+        <v>1.924</v>
       </c>
       <c r="T2">
-        <v>0.205846739318457</v>
+        <v>0.3668954996186117</v>
       </c>
       <c r="U2">
-        <v>108.37</v>
+        <v>93.471</v>
       </c>
       <c r="V2">
-        <v>0.4872751798561151</v>
+        <v>0.708650492797574</v>
       </c>
       <c r="W2">
-        <v>0.00805</v>
+        <v>-0.1254275940706955</v>
       </c>
       <c r="X2">
-        <v>0.07172910137563272</v>
+        <v>0.1166239252446017</v>
       </c>
       <c r="Y2">
-        <v>-0.06367910137563272</v>
+        <v>-0.2420515193152972</v>
       </c>
       <c r="Z2">
-        <v>4.354948942671061</v>
+        <v>4.307707490377974</v>
       </c>
       <c r="AA2">
-        <v>-0.07717123735786756</v>
+        <v>-0.08297758804695839</v>
       </c>
       <c r="AB2">
-        <v>0.06813149760347088</v>
+        <v>0.1106030009950596</v>
       </c>
       <c r="AC2">
-        <v>-0.1453027349613384</v>
+        <v>-0.193580589042018</v>
       </c>
       <c r="AD2">
-        <v>22.37</v>
+        <v>11.83</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>22.37</v>
+        <v>11.83</v>
       </c>
       <c r="AG2">
-        <v>-86</v>
+        <v>-81.64100000000001</v>
       </c>
       <c r="AH2">
-        <v>0.09139191894431507</v>
+        <v>0.08230710359702219</v>
       </c>
       <c r="AI2">
-        <v>0.1046941545373707</v>
+        <v>0.06271536871123362</v>
       </c>
       <c r="AJ2">
-        <v>-0.6304985337243402</v>
+        <v>-1.624405579100261</v>
       </c>
       <c r="AK2">
-        <v>-0.8167141500474833</v>
+        <v>-0.8579430216795049</v>
       </c>
       <c r="AL2">
-        <v>0.237</v>
+        <v>0.875</v>
       </c>
       <c r="AM2">
-        <v>-0.477</v>
+        <v>0.33</v>
       </c>
       <c r="AN2">
-        <v>4.841991341991343</v>
+        <v>-27.51162790697673</v>
       </c>
       <c r="AO2">
-        <v>-21.60337552742616</v>
+        <v>-10.52571428571428</v>
       </c>
       <c r="AP2">
-        <v>-18.61471861471862</v>
+        <v>189.8627906976744</v>
       </c>
       <c r="AQ2">
-        <v>10.73375262054507</v>
+        <v>-27.9090909090909</v>
       </c>
     </row>
     <row r="3">
@@ -719,115 +721,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.101</v>
+        <v>0.0584</v>
       </c>
       <c r="G3">
-        <v>0.06162300319488818</v>
+        <v>0.06071774423241242</v>
       </c>
       <c r="H3">
-        <v>0.05910543130990415</v>
+        <v>0.05981201936770151</v>
       </c>
       <c r="I3">
-        <v>0.02805111821086262</v>
+        <v>0.03503275420108231</v>
       </c>
       <c r="J3">
-        <v>0.02805111821086262</v>
+        <v>0.03239109516808178</v>
       </c>
       <c r="K3">
-        <v>11.3</v>
+        <v>10.7</v>
       </c>
       <c r="L3">
-        <v>0.03610223642172524</v>
+        <v>0.03047564796354315</v>
       </c>
       <c r="M3">
-        <v>1.8364</v>
+        <v>5.23</v>
       </c>
       <c r="N3">
-        <v>0.02451802403204272</v>
+        <v>0.1324050632911392</v>
       </c>
       <c r="O3">
-        <v>0.1625132743362832</v>
+        <v>0.4887850467289719</v>
       </c>
       <c r="P3">
-        <v>1.8364</v>
+        <v>3.32</v>
       </c>
       <c r="Q3">
-        <v>0.02451802403204272</v>
+        <v>0.08405063291139241</v>
       </c>
       <c r="R3">
-        <v>0.1625132743362832</v>
+        <v>0.3102803738317757</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.3652007648183556</v>
       </c>
       <c r="U3">
-        <v>18.4</v>
+        <v>21.5</v>
       </c>
       <c r="V3">
-        <v>0.2456608811748998</v>
+        <v>0.5443037974683544</v>
       </c>
       <c r="W3">
-        <v>0.2250996015936255</v>
+        <v>0.1725806451612903</v>
       </c>
       <c r="X3">
-        <v>0.07808491601051805</v>
+        <v>0.1229080462109035</v>
       </c>
       <c r="Y3">
-        <v>0.1470146855831074</v>
+        <v>0.04967259895038681</v>
       </c>
       <c r="Z3">
-        <v>5.234113712374581</v>
+        <v>5.988401842060379</v>
       </c>
       <c r="AA3">
-        <v>0.1468227424749164</v>
+        <v>0.193970893970894</v>
       </c>
       <c r="AB3">
-        <v>0.0680315085066624</v>
+        <v>0.1091139117406065</v>
       </c>
       <c r="AC3">
-        <v>0.07879123396825397</v>
+        <v>0.08485698223028745</v>
       </c>
       <c r="AD3">
-        <v>16.8</v>
+        <v>7.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>16.8</v>
+        <v>7.8</v>
       </c>
       <c r="AG3">
-        <v>-1.599999999999998</v>
+        <v>-13.7</v>
       </c>
       <c r="AH3">
-        <v>0.183206106870229</v>
+        <v>0.1649048625792812</v>
       </c>
       <c r="AI3">
-        <v>0.2107904642409034</v>
+        <v>0.1056910569105691</v>
       </c>
       <c r="AJ3">
-        <v>-0.02182810368349247</v>
+        <v>-0.5310077519379844</v>
       </c>
       <c r="AK3">
-        <v>-0.02610114192495918</v>
+        <v>-0.2619502868068834</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="AM3">
-        <v>-0.095</v>
+        <v>0.6709999999999999</v>
       </c>
       <c r="AN3">
-        <v>0.9333333333333333</v>
+        <v>0.3768115942028986</v>
+      </c>
+      <c r="AO3">
+        <v>17.85195936139333</v>
       </c>
       <c r="AP3">
-        <v>-0.08888888888888877</v>
+        <v>-0.6618357487922705</v>
       </c>
       <c r="AQ3">
-        <v>-92.42105263157895</v>
+        <v>18.33084947839047</v>
       </c>
     </row>
     <row r="4">
@@ -847,34 +852,34 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.26</v>
+        <v>-0.312</v>
       </c>
       <c r="G4">
-        <v>-0.04664804469273744</v>
+        <v>-0.02323651452282158</v>
       </c>
       <c r="H4">
-        <v>-0.0905027932960894</v>
+        <v>-0.08174273858921161</v>
       </c>
       <c r="I4">
-        <v>-0.09217877094972067</v>
+        <v>-0.129045643153527</v>
       </c>
       <c r="J4">
-        <v>-0.0839743777238293</v>
+        <v>-0.129045643153527</v>
       </c>
       <c r="K4">
-        <v>0.322</v>
+        <v>-8.07</v>
       </c>
       <c r="L4">
-        <v>0.00899441340782123</v>
+        <v>-0.3348547717842323</v>
       </c>
       <c r="M4">
-        <v>0.476</v>
+        <v>0.014</v>
       </c>
       <c r="N4">
-        <v>0.0206060606060606</v>
+        <v>0.0007865168539325843</v>
       </c>
       <c r="O4">
-        <v>1.478260869565217</v>
+        <v>-0.001734820322180917</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -883,82 +888,82 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>0.476</v>
+        <v>0.014</v>
       </c>
       <c r="T4">
         <v>1</v>
       </c>
       <c r="U4">
-        <v>3.77</v>
+        <v>0.671</v>
       </c>
       <c r="V4">
-        <v>0.1632034632034632</v>
+        <v>0.03769662921348315</v>
       </c>
       <c r="W4">
-        <v>0.00805</v>
+        <v>-0.2048223350253807</v>
       </c>
       <c r="X4">
-        <v>0.07172910137563272</v>
+        <v>0.1166239252446017</v>
       </c>
       <c r="Y4">
-        <v>-0.06367910137563272</v>
+        <v>-0.3214462602699824</v>
       </c>
       <c r="Z4">
-        <v>0.9189855221275284</v>
+        <v>0.6430096051227322</v>
       </c>
       <c r="AA4">
-        <v>-0.07717123735786756</v>
+        <v>-0.08297758804695839</v>
       </c>
       <c r="AB4">
-        <v>0.06813149760347088</v>
+        <v>0.1106030009950596</v>
       </c>
       <c r="AC4">
-        <v>-0.1453027349613384</v>
+        <v>-0.193580589042018</v>
       </c>
       <c r="AD4">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AG4">
-        <v>-1.92</v>
+        <v>0.9789999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.07414829659318636</v>
+        <v>0.08483290488431876</v>
       </c>
       <c r="AI4">
-        <v>0.04378698224852071</v>
+        <v>0.04654442877291961</v>
       </c>
       <c r="AJ4">
-        <v>-0.0906515580736544</v>
+        <v>0.05213270142180094</v>
       </c>
       <c r="AK4">
-        <v>-0.0498960498960499</v>
+        <v>0.02814917047643693</v>
       </c>
       <c r="AL4">
-        <v>0.015</v>
+        <v>0.031</v>
       </c>
       <c r="AM4">
-        <v>-0.467</v>
+        <v>-0.29</v>
       </c>
       <c r="AN4">
-        <v>-0.6006493506493507</v>
+        <v>-0.5631399317406143</v>
       </c>
       <c r="AO4">
-        <v>-220</v>
+        <v>-100.3225806451613</v>
       </c>
       <c r="AP4">
-        <v>0.6233766233766234</v>
+        <v>-0.3341296928327644</v>
       </c>
       <c r="AQ4">
-        <v>7.066381156316917</v>
+        <v>10.72413793103448</v>
       </c>
     </row>
     <row r="5">
@@ -978,25 +983,25 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.00025</v>
+        <v>-0.0258</v>
       </c>
       <c r="G5">
-        <v>0.04970414201183431</v>
+        <v>-0.05220228384991842</v>
       </c>
       <c r="H5">
-        <v>-0.1218934911242604</v>
+        <v>-0.2969004893964111</v>
       </c>
       <c r="I5">
-        <v>-0.1254437869822485</v>
+        <v>-0.300163132137031</v>
       </c>
       <c r="J5">
-        <v>-0.1254437869822485</v>
+        <v>-0.300163132137031</v>
       </c>
       <c r="K5">
-        <v>-7.67</v>
+        <v>-11</v>
       </c>
       <c r="L5">
-        <v>-0.09076923076923077</v>
+        <v>-0.1794453507340946</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1020,73 +1025,8785 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>86.2</v>
+        <v>71.3</v>
       </c>
       <c r="V5">
-        <v>0.6929260450160771</v>
+        <v>0.9557640750670242</v>
       </c>
       <c r="W5">
-        <v>-0.08336956521739131</v>
+        <v>-0.1254275940706955</v>
       </c>
       <c r="X5">
-        <v>0.06951740577190493</v>
+        <v>0.1129776030162717</v>
       </c>
       <c r="Y5">
-        <v>-0.1528869709892962</v>
+        <v>-0.2384051970869673</v>
       </c>
       <c r="Z5">
-        <v>114.1891891891878</v>
+        <v>11.74329501915709</v>
       </c>
       <c r="AA5">
-        <v>-14.32432432432415</v>
+        <v>-3.524904214559387</v>
       </c>
       <c r="AB5">
-        <v>0.06817285924304022</v>
+        <v>0.1106984360225236</v>
       </c>
       <c r="AC5">
-        <v>-14.39249718356719</v>
+        <v>-3.635602650581911</v>
       </c>
       <c r="AD5">
-        <v>3.72</v>
+        <v>2.38</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>3.72</v>
+        <v>2.38</v>
       </c>
       <c r="AG5">
-        <v>-82.48</v>
+        <v>-68.92</v>
       </c>
       <c r="AH5">
-        <v>0.02903527942553856</v>
+        <v>0.03091712133021564</v>
       </c>
       <c r="AI5">
-        <v>0.04055822067160925</v>
+        <v>0.02998236331569665</v>
       </c>
       <c r="AJ5">
-        <v>-1.967557251908397</v>
+        <v>-12.13380281690142</v>
       </c>
       <c r="AK5">
-        <v>-14.94202898550726</v>
+        <v>-8.529702970297032</v>
       </c>
       <c r="AL5">
-        <v>0.222</v>
+        <v>0.155</v>
       </c>
       <c r="AM5">
-        <v>0.08499999999999999</v>
+        <v>-0.05099999999999999</v>
       </c>
       <c r="AN5">
-        <v>-0.3611650485436893</v>
+        <v>-0.1307692307692308</v>
       </c>
       <c r="AO5">
-        <v>-47.74774774774774</v>
+        <v>-118.7096774193548</v>
       </c>
       <c r="AP5">
-        <v>8.007766990291262</v>
+        <v>3.786813186813187</v>
       </c>
       <c r="AQ5">
-        <v>-124.7058823529412</v>
+        <v>360.7843137254902</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Broadway Industrial Group Limited (SGX:B69)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SGX:B69</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Computers/Peripherals</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.164904862579281</v>
+      </c>
+      <c r="F2">
+        <v>0.53</v>
+      </c>
+      <c r="G2">
+        <v>39.5</v>
+      </c>
+      <c r="H2">
+        <v>22.7768558975149</v>
+      </c>
+      <c r="I2">
+        <v>25.8</v>
+      </c>
+      <c r="J2">
+        <v>26.3458558975149</v>
+      </c>
+      <c r="K2">
+        <v>7.8</v>
+      </c>
+      <c r="L2">
+        <v>25.069</v>
+      </c>
+      <c r="M2">
+        <v>0.109113911740607</v>
+      </c>
+      <c r="N2">
+        <v>0.104796336826215</v>
+      </c>
+      <c r="O2">
+        <v>0.039259</v>
+      </c>
+      <c r="P2">
+        <v>0.039259</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.122908046210904</v>
+      </c>
+      <c r="T2">
+        <v>0.178700142183435</v>
+      </c>
+      <c r="U2">
+        <v>1.42212764089975</v>
+      </c>
+      <c r="V2">
+        <v>2.36547950080758</v>
+      </c>
+      <c r="W2">
+        <v>10.37306168168245</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>39.5</v>
+      </c>
+      <c r="AB2">
+        <v>0.0591424031092525</v>
+      </c>
+      <c r="AC2">
+        <v>0.0473</v>
+      </c>
+      <c r="AD2">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>20.7</v>
+      </c>
+      <c r="AH2">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="AI2">
+        <v>12.64</v>
+      </c>
+      <c r="AJ2">
+        <v>7.8</v>
+      </c>
+      <c r="AK2">
+        <v>7.8</v>
+      </c>
+      <c r="AL2">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="AM2">
+        <v>7.8</v>
+      </c>
+      <c r="AN2">
+        <v>21.5</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.111064058496774</v>
+      </c>
+      <c r="C2">
+        <v>47.06079652138076</v>
+      </c>
+      <c r="D2">
+        <v>25.56079652138076</v>
+      </c>
+      <c r="E2">
+        <v>-7.8</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>21.5</v>
+      </c>
+      <c r="H2">
+        <v>39.5</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>20.7</v>
+      </c>
+      <c r="K2">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L2">
+        <v>12.3</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>12.3</v>
+      </c>
+      <c r="O2">
+        <v>2.090999999999999</v>
+      </c>
+      <c r="P2">
+        <v>10.209</v>
+      </c>
+      <c r="Q2">
+        <v>18.609</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.111064058496774</v>
+      </c>
+      <c r="T2">
+        <v>1.221865441674431</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W2">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1109325195973295</v>
+      </c>
+      <c r="C3">
+        <v>46.60379139288189</v>
+      </c>
+      <c r="D3">
+        <v>25.57679139288188</v>
+      </c>
+      <c r="E3">
+        <v>-7.327</v>
+      </c>
+      <c r="F3">
+        <v>0.473</v>
+      </c>
+      <c r="G3">
+        <v>21.5</v>
+      </c>
+      <c r="H3">
+        <v>39.5</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>20.7</v>
+      </c>
+      <c r="K3">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L3">
+        <v>12.3</v>
+      </c>
+      <c r="M3">
+        <v>0.0216161</v>
+      </c>
+      <c r="N3">
+        <v>12.2783839</v>
+      </c>
+      <c r="O3">
+        <v>2.087325262999999</v>
+      </c>
+      <c r="P3">
+        <v>10.191058637</v>
+      </c>
+      <c r="Q3">
+        <v>18.591058637</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1116699086841712</v>
+      </c>
+      <c r="T3">
+        <v>1.232109364064226</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W3">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>569.020313562576</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.110800980697885</v>
+      </c>
+      <c r="C4">
+        <v>46.14680629475301</v>
+      </c>
+      <c r="D4">
+        <v>25.592806294753</v>
+      </c>
+      <c r="E4">
+        <v>-6.854</v>
+      </c>
+      <c r="F4">
+        <v>0.946</v>
+      </c>
+      <c r="G4">
+        <v>21.5</v>
+      </c>
+      <c r="H4">
+        <v>39.5</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>20.7</v>
+      </c>
+      <c r="K4">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L4">
+        <v>12.3</v>
+      </c>
+      <c r="M4">
+        <v>0.04323220000000001</v>
+      </c>
+      <c r="N4">
+        <v>12.2567678</v>
+      </c>
+      <c r="O4">
+        <v>2.083650525999999</v>
+      </c>
+      <c r="P4">
+        <v>10.173117274</v>
+      </c>
+      <c r="Q4">
+        <v>18.573117274</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1122881231611071</v>
+      </c>
+      <c r="T4">
+        <v>1.24256234609463</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W4">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>284.510156781288</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1106694417984405</v>
+      </c>
+      <c r="C5">
+        <v>45.68984126464375</v>
+      </c>
+      <c r="D5">
+        <v>25.60884126464374</v>
+      </c>
+      <c r="E5">
+        <v>-6.381</v>
+      </c>
+      <c r="F5">
+        <v>1.419</v>
+      </c>
+      <c r="G5">
+        <v>21.5</v>
+      </c>
+      <c r="H5">
+        <v>39.5</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>20.7</v>
+      </c>
+      <c r="K5">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L5">
+        <v>12.3</v>
+      </c>
+      <c r="M5">
+        <v>0.0648483</v>
+      </c>
+      <c r="N5">
+        <v>12.2351517</v>
+      </c>
+      <c r="O5">
+        <v>2.079975788999999</v>
+      </c>
+      <c r="P5">
+        <v>10.155175911</v>
+      </c>
+      <c r="Q5">
+        <v>18.555175911</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1129190843282891</v>
+      </c>
+      <c r="T5">
+        <v>1.253230853527723</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W5">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>189.673437854192</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.110537902898996</v>
+      </c>
+      <c r="C6">
+        <v>45.2328963402981</v>
+      </c>
+      <c r="D6">
+        <v>25.62489634029811</v>
+      </c>
+      <c r="E6">
+        <v>-5.907999999999999</v>
+      </c>
+      <c r="F6">
+        <v>1.892</v>
+      </c>
+      <c r="G6">
+        <v>21.5</v>
+      </c>
+      <c r="H6">
+        <v>39.5</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>20.7</v>
+      </c>
+      <c r="K6">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L6">
+        <v>12.3</v>
+      </c>
+      <c r="M6">
+        <v>0.08646440000000001</v>
+      </c>
+      <c r="N6">
+        <v>12.2135356</v>
+      </c>
+      <c r="O6">
+        <v>2.076301051999999</v>
+      </c>
+      <c r="P6">
+        <v>10.137234548</v>
+      </c>
+      <c r="Q6">
+        <v>18.537234548</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1135631905197875</v>
+      </c>
+      <c r="T6">
+        <v>1.264121621532338</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W6">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>142.255078390644</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1104063639995514</v>
+      </c>
+      <c r="C7">
+        <v>44.77597155955485</v>
+      </c>
+      <c r="D7">
+        <v>25.64097155955485</v>
+      </c>
+      <c r="E7">
+        <v>-5.435</v>
+      </c>
+      <c r="F7">
+        <v>2.365</v>
+      </c>
+      <c r="G7">
+        <v>21.5</v>
+      </c>
+      <c r="H7">
+        <v>39.5</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>20.7</v>
+      </c>
+      <c r="K7">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L7">
+        <v>12.3</v>
+      </c>
+      <c r="M7">
+        <v>0.1080805</v>
+      </c>
+      <c r="N7">
+        <v>12.1919195</v>
+      </c>
+      <c r="O7">
+        <v>2.072626314999999</v>
+      </c>
+      <c r="P7">
+        <v>10.119293185</v>
+      </c>
+      <c r="Q7">
+        <v>18.519293185</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1142208568416331</v>
+      </c>
+      <c r="T7">
+        <v>1.275241668863366</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W7">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>113.8040627125152</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1102748251001069</v>
+      </c>
+      <c r="C8">
+        <v>44.3190669603477</v>
+      </c>
+      <c r="D8">
+        <v>25.65706696034771</v>
+      </c>
+      <c r="E8">
+        <v>-4.962</v>
+      </c>
+      <c r="F8">
+        <v>2.838</v>
+      </c>
+      <c r="G8">
+        <v>21.5</v>
+      </c>
+      <c r="H8">
+        <v>39.5</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>20.7</v>
+      </c>
+      <c r="K8">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L8">
+        <v>12.3</v>
+      </c>
+      <c r="M8">
+        <v>0.1296966</v>
+      </c>
+      <c r="N8">
+        <v>12.1703034</v>
+      </c>
+      <c r="O8">
+        <v>2.068951577999999</v>
+      </c>
+      <c r="P8">
+        <v>10.101351822</v>
+      </c>
+      <c r="Q8">
+        <v>18.501351822</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1148925160639435</v>
+      </c>
+      <c r="T8">
+        <v>1.286598312946118</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W8">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>94.83671892709602</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1101432862006624</v>
+      </c>
+      <c r="C9">
+        <v>43.86218258070573</v>
+      </c>
+      <c r="D9">
+        <v>25.67318258070573</v>
+      </c>
+      <c r="E9">
+        <v>-4.489</v>
+      </c>
+      <c r="F9">
+        <v>3.311</v>
+      </c>
+      <c r="G9">
+        <v>21.5</v>
+      </c>
+      <c r="H9">
+        <v>39.5</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>20.7</v>
+      </c>
+      <c r="K9">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L9">
+        <v>12.3</v>
+      </c>
+      <c r="M9">
+        <v>0.1513127</v>
+      </c>
+      <c r="N9">
+        <v>12.1486873</v>
+      </c>
+      <c r="O9">
+        <v>2.065276840999999</v>
+      </c>
+      <c r="P9">
+        <v>10.083410459</v>
+      </c>
+      <c r="Q9">
+        <v>18.483410459</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1155786195706047</v>
+      </c>
+      <c r="T9">
+        <v>1.298199185933876</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W9">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>81.28861622322515</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1100117473012179</v>
+      </c>
+      <c r="C10">
+        <v>43.40531845875357</v>
+      </c>
+      <c r="D10">
+        <v>25.68931845875357</v>
+      </c>
+      <c r="E10">
+        <v>-4.016</v>
+      </c>
+      <c r="F10">
+        <v>3.784</v>
+      </c>
+      <c r="G10">
+        <v>21.5</v>
+      </c>
+      <c r="H10">
+        <v>39.5</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>20.7</v>
+      </c>
+      <c r="K10">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L10">
+        <v>12.3</v>
+      </c>
+      <c r="M10">
+        <v>0.1729288</v>
+      </c>
+      <c r="N10">
+        <v>12.1270712</v>
+      </c>
+      <c r="O10">
+        <v>2.061602103999999</v>
+      </c>
+      <c r="P10">
+        <v>10.065469096</v>
+      </c>
+      <c r="Q10">
+        <v>18.465469096</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.116279638370889</v>
+      </c>
+      <c r="T10">
+        <v>1.310052251812672</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W10">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>71.127539195322</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1098802084017734</v>
+      </c>
+      <c r="C11">
+        <v>42.94847463271181</v>
+      </c>
+      <c r="D11">
+        <v>25.70547463271181</v>
+      </c>
+      <c r="E11">
+        <v>-3.543</v>
+      </c>
+      <c r="F11">
+        <v>4.257</v>
+      </c>
+      <c r="G11">
+        <v>21.5</v>
+      </c>
+      <c r="H11">
+        <v>39.5</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>20.7</v>
+      </c>
+      <c r="K11">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L11">
+        <v>12.3</v>
+      </c>
+      <c r="M11">
+        <v>0.1945449</v>
+      </c>
+      <c r="N11">
+        <v>12.1054551</v>
+      </c>
+      <c r="O11">
+        <v>2.057927366999999</v>
+      </c>
+      <c r="P11">
+        <v>10.047527733</v>
+      </c>
+      <c r="Q11">
+        <v>18.447527733</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1169960641777729</v>
+      </c>
+      <c r="T11">
+        <v>1.322165824633859</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W11">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>63.22447928473068</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1097486695023289</v>
+      </c>
+      <c r="C12">
+        <v>42.49165114089721</v>
+      </c>
+      <c r="D12">
+        <v>25.7216511408972</v>
+      </c>
+      <c r="E12">
+        <v>-3.07</v>
+      </c>
+      <c r="F12">
+        <v>4.73</v>
+      </c>
+      <c r="G12">
+        <v>21.5</v>
+      </c>
+      <c r="H12">
+        <v>39.5</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>20.7</v>
+      </c>
+      <c r="K12">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L12">
+        <v>12.3</v>
+      </c>
+      <c r="M12">
+        <v>0.216161</v>
+      </c>
+      <c r="N12">
+        <v>12.083839</v>
+      </c>
+      <c r="O12">
+        <v>2.054252629999999</v>
+      </c>
+      <c r="P12">
+        <v>10.02958637</v>
+      </c>
+      <c r="Q12">
+        <v>18.42958637</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1177284105581432</v>
+      </c>
+      <c r="T12">
+        <v>1.334548587962184</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W12">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>56.90203135625761</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1096171306028843</v>
+      </c>
+      <c r="C13">
+        <v>42.03484802172305</v>
+      </c>
+      <c r="D13">
+        <v>25.73784802172306</v>
+      </c>
+      <c r="E13">
+        <v>-2.597</v>
+      </c>
+      <c r="F13">
+        <v>5.202999999999999</v>
+      </c>
+      <c r="G13">
+        <v>21.5</v>
+      </c>
+      <c r="H13">
+        <v>39.5</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>20.7</v>
+      </c>
+      <c r="K13">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L13">
+        <v>12.3</v>
+      </c>
+      <c r="M13">
+        <v>0.2377771</v>
+      </c>
+      <c r="N13">
+        <v>12.0622229</v>
+      </c>
+      <c r="O13">
+        <v>2.050577892999999</v>
+      </c>
+      <c r="P13">
+        <v>10.011645007</v>
+      </c>
+      <c r="Q13">
+        <v>18.411645007</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1184772141605442</v>
+      </c>
+      <c r="T13">
+        <v>1.347209615634965</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W13">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>51.72911941477964</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1094855917034398</v>
+      </c>
+      <c r="C14">
+        <v>41.57806531369946</v>
+      </c>
+      <c r="D14">
+        <v>25.75406531369946</v>
+      </c>
+      <c r="E14">
+        <v>-2.124000000000001</v>
+      </c>
+      <c r="F14">
+        <v>5.675999999999999</v>
+      </c>
+      <c r="G14">
+        <v>21.5</v>
+      </c>
+      <c r="H14">
+        <v>39.5</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>20.7</v>
+      </c>
+      <c r="K14">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L14">
+        <v>12.3</v>
+      </c>
+      <c r="M14">
+        <v>0.2593932</v>
+      </c>
+      <c r="N14">
+        <v>12.0406068</v>
+      </c>
+      <c r="O14">
+        <v>2.046903156</v>
+      </c>
+      <c r="P14">
+        <v>9.993703644000002</v>
+      </c>
+      <c r="Q14">
+        <v>18.393703644</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1192430360266362</v>
+      </c>
+      <c r="T14">
+        <v>1.360158393936673</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W14">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>47.41835946354801</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1093540528039953</v>
+      </c>
+      <c r="C15">
+        <v>41.12130305543364</v>
+      </c>
+      <c r="D15">
+        <v>25.77030305543364</v>
+      </c>
+      <c r="E15">
+        <v>-1.651</v>
+      </c>
+      <c r="F15">
+        <v>6.149</v>
+      </c>
+      <c r="G15">
+        <v>21.5</v>
+      </c>
+      <c r="H15">
+        <v>39.5</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>20.7</v>
+      </c>
+      <c r="K15">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L15">
+        <v>12.3</v>
+      </c>
+      <c r="M15">
+        <v>0.2810093</v>
+      </c>
+      <c r="N15">
+        <v>12.0189907</v>
+      </c>
+      <c r="O15">
+        <v>2.043228418999999</v>
+      </c>
+      <c r="P15">
+        <v>9.975762281000002</v>
+      </c>
+      <c r="Q15">
+        <v>18.375762281</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1200264629930981</v>
+      </c>
+      <c r="T15">
+        <v>1.373404845302788</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W15">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>43.77079335096739</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1092225139045508</v>
+      </c>
+      <c r="C16">
+        <v>40.66456128563026</v>
+      </c>
+      <c r="D16">
+        <v>25.78656128563026</v>
+      </c>
+      <c r="E16">
+        <v>-1.178</v>
+      </c>
+      <c r="F16">
+        <v>6.622</v>
+      </c>
+      <c r="G16">
+        <v>21.5</v>
+      </c>
+      <c r="H16">
+        <v>39.5</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>20.7</v>
+      </c>
+      <c r="K16">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L16">
+        <v>12.3</v>
+      </c>
+      <c r="M16">
+        <v>0.3026254</v>
+      </c>
+      <c r="N16">
+        <v>11.9973746</v>
+      </c>
+      <c r="O16">
+        <v>2.039553681999999</v>
+      </c>
+      <c r="P16">
+        <v>9.957820918000001</v>
+      </c>
+      <c r="Q16">
+        <v>18.357820918</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1208281091913381</v>
+      </c>
+      <c r="T16">
+        <v>1.386959353677418</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W16">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>40.64430811161257</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1090909750051063</v>
+      </c>
+      <c r="C17">
+        <v>40.20784004309169</v>
+      </c>
+      <c r="D17">
+        <v>25.8028400430917</v>
+      </c>
+      <c r="E17">
+        <v>-0.7050000000000001</v>
+      </c>
+      <c r="F17">
+        <v>7.095</v>
+      </c>
+      <c r="G17">
+        <v>21.5</v>
+      </c>
+      <c r="H17">
+        <v>39.5</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>20.7</v>
+      </c>
+      <c r="K17">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L17">
+        <v>12.3</v>
+      </c>
+      <c r="M17">
+        <v>0.3242415</v>
+      </c>
+      <c r="N17">
+        <v>11.9757585</v>
+      </c>
+      <c r="O17">
+        <v>2.035878944999999</v>
+      </c>
+      <c r="P17">
+        <v>9.939879555000001</v>
+      </c>
+      <c r="Q17">
+        <v>18.339879555</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1216486176530662</v>
+      </c>
+      <c r="T17">
+        <v>1.400832791660862</v>
+      </c>
+      <c r="U17">
+        <v>0.0457</v>
+      </c>
+      <c r="V17">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W17">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>37.93468757083841</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1089594361056618</v>
+      </c>
+      <c r="C18">
+        <v>39.75113936671838</v>
+      </c>
+      <c r="D18">
+        <v>25.81913936671837</v>
+      </c>
+      <c r="E18">
+        <v>-0.2320000000000002</v>
+      </c>
+      <c r="F18">
+        <v>7.568</v>
+      </c>
+      <c r="G18">
+        <v>21.5</v>
+      </c>
+      <c r="H18">
+        <v>39.5</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>20.7</v>
+      </c>
+      <c r="K18">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L18">
+        <v>12.3</v>
+      </c>
+      <c r="M18">
+        <v>0.3458576</v>
+      </c>
+      <c r="N18">
+        <v>11.9541424</v>
+      </c>
+      <c r="O18">
+        <v>2.032204207999999</v>
+      </c>
+      <c r="P18">
+        <v>9.921938192000001</v>
+      </c>
+      <c r="Q18">
+        <v>18.321938192</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1224886620305497</v>
+      </c>
+      <c r="T18">
+        <v>1.415036549596293</v>
+      </c>
+      <c r="U18">
+        <v>0.0457</v>
+      </c>
+      <c r="V18">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W18">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>35.563769597661</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1088278972062172</v>
+      </c>
+      <c r="C19">
+        <v>39.29445929550909</v>
+      </c>
+      <c r="D19">
+        <v>25.83545929550909</v>
+      </c>
+      <c r="E19">
+        <v>0.2410000000000005</v>
+      </c>
+      <c r="F19">
+        <v>8.041</v>
+      </c>
+      <c r="G19">
+        <v>21.5</v>
+      </c>
+      <c r="H19">
+        <v>39.5</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>20.7</v>
+      </c>
+      <c r="K19">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L19">
+        <v>12.3</v>
+      </c>
+      <c r="M19">
+        <v>0.3674737000000001</v>
+      </c>
+      <c r="N19">
+        <v>11.9325263</v>
+      </c>
+      <c r="O19">
+        <v>2.028529470999999</v>
+      </c>
+      <c r="P19">
+        <v>9.903996829000002</v>
+      </c>
+      <c r="Q19">
+        <v>18.303996829</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1233489484412256</v>
+      </c>
+      <c r="T19">
+        <v>1.429582566759084</v>
+      </c>
+      <c r="U19">
+        <v>0.0457</v>
+      </c>
+      <c r="V19">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W19">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>33.47178315073976</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1086963583067727</v>
+      </c>
+      <c r="C20">
+        <v>38.83779986856129</v>
+      </c>
+      <c r="D20">
+        <v>25.85179986856129</v>
+      </c>
+      <c r="E20">
+        <v>0.7139999999999995</v>
+      </c>
+      <c r="F20">
+        <v>8.513999999999999</v>
+      </c>
+      <c r="G20">
+        <v>21.5</v>
+      </c>
+      <c r="H20">
+        <v>39.5</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>20.7</v>
+      </c>
+      <c r="K20">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L20">
+        <v>12.3</v>
+      </c>
+      <c r="M20">
+        <v>0.3890898</v>
+      </c>
+      <c r="N20">
+        <v>11.9109102</v>
+      </c>
+      <c r="O20">
+        <v>2.024854733999999</v>
+      </c>
+      <c r="P20">
+        <v>9.886055466000002</v>
+      </c>
+      <c r="Q20">
+        <v>18.286055466</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1242302174472838</v>
+      </c>
+      <c r="T20">
+        <v>1.444483364828284</v>
+      </c>
+      <c r="U20">
+        <v>0.0457</v>
+      </c>
+      <c r="V20">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W20">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>31.61223964236534</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1085648194073282</v>
+      </c>
+      <c r="C21">
+        <v>38.38116112507139</v>
+      </c>
+      <c r="D21">
+        <v>25.86816112507139</v>
+      </c>
+      <c r="E21">
+        <v>1.187</v>
+      </c>
+      <c r="F21">
+        <v>8.987</v>
+      </c>
+      <c r="G21">
+        <v>21.5</v>
+      </c>
+      <c r="H21">
+        <v>39.5</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>20.7</v>
+      </c>
+      <c r="K21">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L21">
+        <v>12.3</v>
+      </c>
+      <c r="M21">
+        <v>0.4107059000000001</v>
+      </c>
+      <c r="N21">
+        <v>11.8892941</v>
+      </c>
+      <c r="O21">
+        <v>2.021179996999999</v>
+      </c>
+      <c r="P21">
+        <v>9.868114103000002</v>
+      </c>
+      <c r="Q21">
+        <v>18.268114103</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1251332461818867</v>
+      </c>
+      <c r="T21">
+        <v>1.459752083837465</v>
+      </c>
+      <c r="U21">
+        <v>0.0457</v>
+      </c>
+      <c r="V21">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W21">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>29.94843755592505</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1084332805078837</v>
+      </c>
+      <c r="C22">
+        <v>37.92454310433512</v>
+      </c>
+      <c r="D22">
+        <v>25.88454310433513</v>
+      </c>
+      <c r="E22">
+        <v>1.659999999999999</v>
+      </c>
+      <c r="F22">
+        <v>9.459999999999999</v>
+      </c>
+      <c r="G22">
+        <v>21.5</v>
+      </c>
+      <c r="H22">
+        <v>39.5</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>20.7</v>
+      </c>
+      <c r="K22">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L22">
+        <v>12.3</v>
+      </c>
+      <c r="M22">
+        <v>0.432322</v>
+      </c>
+      <c r="N22">
+        <v>11.867678</v>
+      </c>
+      <c r="O22">
+        <v>2.01750526</v>
+      </c>
+      <c r="P22">
+        <v>9.850172740000001</v>
+      </c>
+      <c r="Q22">
+        <v>18.25017274</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1260588506348546</v>
+      </c>
+      <c r="T22">
+        <v>1.475402520821875</v>
+      </c>
+      <c r="U22">
+        <v>0.0457</v>
+      </c>
+      <c r="V22">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W22">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>28.45101567812881</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1083017416084392</v>
+      </c>
+      <c r="C23">
+        <v>37.46794584574781</v>
+      </c>
+      <c r="D23">
+        <v>25.90094584574781</v>
+      </c>
+      <c r="E23">
+        <v>2.133</v>
+      </c>
+      <c r="F23">
+        <v>9.933</v>
+      </c>
+      <c r="G23">
+        <v>21.5</v>
+      </c>
+      <c r="H23">
+        <v>39.5</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>20.7</v>
+      </c>
+      <c r="K23">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L23">
+        <v>12.3</v>
+      </c>
+      <c r="M23">
+        <v>0.4539381</v>
+      </c>
+      <c r="N23">
+        <v>11.8460619</v>
+      </c>
+      <c r="O23">
+        <v>2.013830522999999</v>
+      </c>
+      <c r="P23">
+        <v>9.832231377000001</v>
+      </c>
+      <c r="Q23">
+        <v>18.232231377</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1270078881119484</v>
+      </c>
+      <c r="T23">
+        <v>1.491449171400827</v>
+      </c>
+      <c r="U23">
+        <v>0.0457</v>
+      </c>
+      <c r="V23">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W23">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>27.09620540774172</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1081702027089947</v>
+      </c>
+      <c r="C24">
+        <v>37.01136938880467</v>
+      </c>
+      <c r="D24">
+        <v>25.91736938880467</v>
+      </c>
+      <c r="E24">
+        <v>2.605999999999999</v>
+      </c>
+      <c r="F24">
+        <v>10.406</v>
+      </c>
+      <c r="G24">
+        <v>21.5</v>
+      </c>
+      <c r="H24">
+        <v>39.5</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>20.7</v>
+      </c>
+      <c r="K24">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L24">
+        <v>12.3</v>
+      </c>
+      <c r="M24">
+        <v>0.4755542</v>
+      </c>
+      <c r="N24">
+        <v>11.8244458</v>
+      </c>
+      <c r="O24">
+        <v>2.010155785999999</v>
+      </c>
+      <c r="P24">
+        <v>9.814290014000001</v>
+      </c>
+      <c r="Q24">
+        <v>18.214290014</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1279812598833265</v>
+      </c>
+      <c r="T24">
+        <v>1.507907274558727</v>
+      </c>
+      <c r="U24">
+        <v>0.0457</v>
+      </c>
+      <c r="V24">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W24">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>25.86455970738982</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1080386638095502</v>
+      </c>
+      <c r="C25">
+        <v>36.55481377310122</v>
+      </c>
+      <c r="D25">
+        <v>25.93381377310122</v>
+      </c>
+      <c r="E25">
+        <v>3.079</v>
+      </c>
+      <c r="F25">
+        <v>10.879</v>
+      </c>
+      <c r="G25">
+        <v>21.5</v>
+      </c>
+      <c r="H25">
+        <v>39.5</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>20.7</v>
+      </c>
+      <c r="K25">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L25">
+        <v>12.3</v>
+      </c>
+      <c r="M25">
+        <v>0.4971703</v>
+      </c>
+      <c r="N25">
+        <v>11.8028297</v>
+      </c>
+      <c r="O25">
+        <v>2.006481048999999</v>
+      </c>
+      <c r="P25">
+        <v>9.796348651000001</v>
+      </c>
+      <c r="Q25">
+        <v>18.196348651</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1289799140383768</v>
+      </c>
+      <c r="T25">
+        <v>1.524792860915533</v>
+      </c>
+      <c r="U25">
+        <v>0.0457</v>
+      </c>
+      <c r="V25">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W25">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>24.74001363315548</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1079071249101057</v>
+      </c>
+      <c r="C26">
+        <v>36.09827903833347</v>
+      </c>
+      <c r="D26">
+        <v>25.95027903833347</v>
+      </c>
+      <c r="E26">
+        <v>3.551999999999999</v>
+      </c>
+      <c r="F26">
+        <v>11.352</v>
+      </c>
+      <c r="G26">
+        <v>21.5</v>
+      </c>
+      <c r="H26">
+        <v>39.5</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>20.7</v>
+      </c>
+      <c r="K26">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L26">
+        <v>12.3</v>
+      </c>
+      <c r="M26">
+        <v>0.5187864</v>
+      </c>
+      <c r="N26">
+        <v>11.7812136</v>
+      </c>
+      <c r="O26">
+        <v>2.002806311999999</v>
+      </c>
+      <c r="P26">
+        <v>9.778407288000002</v>
+      </c>
+      <c r="Q26">
+        <v>18.178407288</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1300048485659285</v>
+      </c>
+      <c r="T26">
+        <v>1.542122804808044</v>
+      </c>
+      <c r="U26">
+        <v>0.0457</v>
+      </c>
+      <c r="V26">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W26">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>23.709179731774</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1077755860106611</v>
+      </c>
+      <c r="C27">
+        <v>35.64176522429834</v>
+      </c>
+      <c r="D27">
+        <v>25.96676522429834</v>
+      </c>
+      <c r="E27">
+        <v>4.024999999999999</v>
+      </c>
+      <c r="F27">
+        <v>11.825</v>
+      </c>
+      <c r="G27">
+        <v>21.5</v>
+      </c>
+      <c r="H27">
+        <v>39.5</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>20.7</v>
+      </c>
+      <c r="K27">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L27">
+        <v>12.3</v>
+      </c>
+      <c r="M27">
+        <v>0.5404025</v>
+      </c>
+      <c r="N27">
+        <v>11.7595975</v>
+      </c>
+      <c r="O27">
+        <v>1.999131574999999</v>
+      </c>
+      <c r="P27">
+        <v>9.760465925</v>
+      </c>
+      <c r="Q27">
+        <v>18.160465925</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1310571146808815</v>
+      </c>
+      <c r="T27">
+        <v>1.55991488053769</v>
+      </c>
+      <c r="U27">
+        <v>0.0457</v>
+      </c>
+      <c r="V27">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W27">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>22.76081254250304</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1076440471112166</v>
+      </c>
+      <c r="C28">
+        <v>35.18527237089393</v>
+      </c>
+      <c r="D28">
+        <v>25.98327237089393</v>
+      </c>
+      <c r="E28">
+        <v>4.498</v>
+      </c>
+      <c r="F28">
+        <v>12.298</v>
+      </c>
+      <c r="G28">
+        <v>21.5</v>
+      </c>
+      <c r="H28">
+        <v>39.5</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>20.7</v>
+      </c>
+      <c r="K28">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L28">
+        <v>12.3</v>
+      </c>
+      <c r="M28">
+        <v>0.5620186</v>
+      </c>
+      <c r="N28">
+        <v>11.7379814</v>
+      </c>
+      <c r="O28">
+        <v>1.995456837999999</v>
+      </c>
+      <c r="P28">
+        <v>9.742524562000002</v>
+      </c>
+      <c r="Q28">
+        <v>18.142524562</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.132137820420563</v>
+      </c>
+      <c r="T28">
+        <v>1.578187823178947</v>
+      </c>
+      <c r="U28">
+        <v>0.0457</v>
+      </c>
+      <c r="V28">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W28">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>21.88539667548369</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1075125082117721</v>
+      </c>
+      <c r="C29">
+        <v>34.72880051811988</v>
+      </c>
+      <c r="D29">
+        <v>25.99980051811989</v>
+      </c>
+      <c r="E29">
+        <v>4.971000000000001</v>
+      </c>
+      <c r="F29">
+        <v>12.771</v>
+      </c>
+      <c r="G29">
+        <v>21.5</v>
+      </c>
+      <c r="H29">
+        <v>39.5</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>20.7</v>
+      </c>
+      <c r="K29">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L29">
+        <v>12.3</v>
+      </c>
+      <c r="M29">
+        <v>0.5836347000000001</v>
+      </c>
+      <c r="N29">
+        <v>11.7163653</v>
+      </c>
+      <c r="O29">
+        <v>1.991782100999999</v>
+      </c>
+      <c r="P29">
+        <v>9.724583199000001</v>
+      </c>
+      <c r="Q29">
+        <v>18.124583199</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1332481345366741</v>
+      </c>
+      <c r="T29">
+        <v>1.596961394385718</v>
+      </c>
+      <c r="U29">
+        <v>0.0457</v>
+      </c>
+      <c r="V29">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W29">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>21.07482642824356</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1073809693123276</v>
+      </c>
+      <c r="C30">
+        <v>34.27234970607766</v>
+      </c>
+      <c r="D30">
+        <v>26.01634970607765</v>
+      </c>
+      <c r="E30">
+        <v>5.444</v>
+      </c>
+      <c r="F30">
+        <v>13.244</v>
+      </c>
+      <c r="G30">
+        <v>21.5</v>
+      </c>
+      <c r="H30">
+        <v>39.5</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>20.7</v>
+      </c>
+      <c r="K30">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L30">
+        <v>12.3</v>
+      </c>
+      <c r="M30">
+        <v>0.6052508000000001</v>
+      </c>
+      <c r="N30">
+        <v>11.6947492</v>
+      </c>
+      <c r="O30">
+        <v>1.988107363999999</v>
+      </c>
+      <c r="P30">
+        <v>9.706641836000001</v>
+      </c>
+      <c r="Q30">
+        <v>18.106641836</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1343892907115661</v>
+      </c>
+      <c r="T30">
+        <v>1.616256453681566</v>
+      </c>
+      <c r="U30">
+        <v>0.0457</v>
+      </c>
+      <c r="V30">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W30">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>20.32215405580628</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1072494304128831</v>
+      </c>
+      <c r="C31">
+        <v>33.81591997497087</v>
+      </c>
+      <c r="D31">
+        <v>26.03291997497087</v>
+      </c>
+      <c r="E31">
+        <v>5.916999999999999</v>
+      </c>
+      <c r="F31">
+        <v>13.717</v>
+      </c>
+      <c r="G31">
+        <v>21.5</v>
+      </c>
+      <c r="H31">
+        <v>39.5</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>20.7</v>
+      </c>
+      <c r="K31">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L31">
+        <v>12.3</v>
+      </c>
+      <c r="M31">
+        <v>0.6268669</v>
+      </c>
+      <c r="N31">
+        <v>11.6731331</v>
+      </c>
+      <c r="O31">
+        <v>1.984432626999999</v>
+      </c>
+      <c r="P31">
+        <v>9.688700473000001</v>
+      </c>
+      <c r="Q31">
+        <v>18.088700473</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1355625921308212</v>
+      </c>
+      <c r="T31">
+        <v>1.636095035774481</v>
+      </c>
+      <c r="U31">
+        <v>0.0457</v>
+      </c>
+      <c r="V31">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W31">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>19.62139012284745</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1071178915134385</v>
+      </c>
+      <c r="C32">
+        <v>33.35951136510567</v>
+      </c>
+      <c r="D32">
+        <v>26.04951136510567</v>
+      </c>
+      <c r="E32">
+        <v>6.39</v>
+      </c>
+      <c r="F32">
+        <v>14.19</v>
+      </c>
+      <c r="G32">
+        <v>21.5</v>
+      </c>
+      <c r="H32">
+        <v>39.5</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>20.7</v>
+      </c>
+      <c r="K32">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L32">
+        <v>12.3</v>
+      </c>
+      <c r="M32">
+        <v>0.648483</v>
+      </c>
+      <c r="N32">
+        <v>11.651517</v>
+      </c>
+      <c r="O32">
+        <v>1.980757889999999</v>
+      </c>
+      <c r="P32">
+        <v>9.670759110000001</v>
+      </c>
+      <c r="Q32">
+        <v>18.07075911</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1367694164477694</v>
+      </c>
+      <c r="T32">
+        <v>1.656500434498621</v>
+      </c>
+      <c r="U32">
+        <v>0.0457</v>
+      </c>
+      <c r="V32">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W32">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>18.9673437854192</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.106986352613994</v>
+      </c>
+      <c r="C33">
+        <v>32.90312391689099</v>
+      </c>
+      <c r="D33">
+        <v>26.06612391689098</v>
+      </c>
+      <c r="E33">
+        <v>6.862999999999999</v>
+      </c>
+      <c r="F33">
+        <v>14.663</v>
+      </c>
+      <c r="G33">
+        <v>21.5</v>
+      </c>
+      <c r="H33">
+        <v>39.5</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>20.7</v>
+      </c>
+      <c r="K33">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L33">
+        <v>12.3</v>
+      </c>
+      <c r="M33">
+        <v>0.6700990999999999</v>
+      </c>
+      <c r="N33">
+        <v>11.6299009</v>
+      </c>
+      <c r="O33">
+        <v>1.977083152999999</v>
+      </c>
+      <c r="P33">
+        <v>9.652817747000002</v>
+      </c>
+      <c r="Q33">
+        <v>18.052817747</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1380112211797015</v>
+      </c>
+      <c r="T33">
+        <v>1.677497294055345</v>
+      </c>
+      <c r="U33">
+        <v>0.0457</v>
+      </c>
+      <c r="V33">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W33">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>18.35549398588955</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1068548137145495</v>
+      </c>
+      <c r="C34">
+        <v>32.44675767083889</v>
+      </c>
+      <c r="D34">
+        <v>26.08275767083889</v>
+      </c>
+      <c r="E34">
+        <v>7.335999999999999</v>
+      </c>
+      <c r="F34">
+        <v>15.136</v>
+      </c>
+      <c r="G34">
+        <v>21.5</v>
+      </c>
+      <c r="H34">
+        <v>39.5</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>20.7</v>
+      </c>
+      <c r="K34">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L34">
+        <v>12.3</v>
+      </c>
+      <c r="M34">
+        <v>0.6917152000000001</v>
+      </c>
+      <c r="N34">
+        <v>11.6082848</v>
+      </c>
+      <c r="O34">
+        <v>1.973408415999999</v>
+      </c>
+      <c r="P34">
+        <v>9.634876384</v>
+      </c>
+      <c r="Q34">
+        <v>18.034876384</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1392895495802199</v>
+      </c>
+      <c r="T34">
+        <v>1.699111708304914</v>
+      </c>
+      <c r="U34">
+        <v>0.0457</v>
+      </c>
+      <c r="V34">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W34">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>17.7818847988305</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.106723274815105</v>
+      </c>
+      <c r="C35">
+        <v>31.99041266756497</v>
+      </c>
+      <c r="D35">
+        <v>26.09941266756497</v>
+      </c>
+      <c r="E35">
+        <v>7.809</v>
+      </c>
+      <c r="F35">
+        <v>15.609</v>
+      </c>
+      <c r="G35">
+        <v>21.5</v>
+      </c>
+      <c r="H35">
+        <v>39.5</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>20.7</v>
+      </c>
+      <c r="K35">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L35">
+        <v>12.3</v>
+      </c>
+      <c r="M35">
+        <v>0.7133313000000001</v>
+      </c>
+      <c r="N35">
+        <v>11.5866687</v>
+      </c>
+      <c r="O35">
+        <v>1.969733678999999</v>
+      </c>
+      <c r="P35">
+        <v>9.616935021000002</v>
+      </c>
+      <c r="Q35">
+        <v>18.016935021</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1406060370374702</v>
+      </c>
+      <c r="T35">
+        <v>1.721371328949993</v>
+      </c>
+      <c r="U35">
+        <v>0.0457</v>
+      </c>
+      <c r="V35">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W35">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>17.24303980492655</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1065917359156605</v>
+      </c>
+      <c r="C36">
+        <v>31.53408894778858</v>
+      </c>
+      <c r="D36">
+        <v>26.11608894778858</v>
+      </c>
+      <c r="E36">
+        <v>8.282</v>
+      </c>
+      <c r="F36">
+        <v>16.082</v>
+      </c>
+      <c r="G36">
+        <v>21.5</v>
+      </c>
+      <c r="H36">
+        <v>39.5</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>20.7</v>
+      </c>
+      <c r="K36">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L36">
+        <v>12.3</v>
+      </c>
+      <c r="M36">
+        <v>0.7349474000000001</v>
+      </c>
+      <c r="N36">
+        <v>11.5650526</v>
+      </c>
+      <c r="O36">
+        <v>1.966058941999999</v>
+      </c>
+      <c r="P36">
+        <v>9.598993658000001</v>
+      </c>
+      <c r="Q36">
+        <v>17.998993658</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.141962418054031</v>
+      </c>
+      <c r="T36">
+        <v>1.744305483554013</v>
+      </c>
+      <c r="U36">
+        <v>0.0457</v>
+      </c>
+      <c r="V36">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W36">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>16.73589157536988</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.106460197016216</v>
+      </c>
+      <c r="C37">
+        <v>31.07778655233323</v>
+      </c>
+      <c r="D37">
+        <v>26.13278655233323</v>
+      </c>
+      <c r="E37">
+        <v>8.754999999999999</v>
+      </c>
+      <c r="F37">
+        <v>16.555</v>
+      </c>
+      <c r="G37">
+        <v>21.5</v>
+      </c>
+      <c r="H37">
+        <v>39.5</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>20.7</v>
+      </c>
+      <c r="K37">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L37">
+        <v>12.3</v>
+      </c>
+      <c r="M37">
+        <v>0.7565635000000001</v>
+      </c>
+      <c r="N37">
+        <v>11.5434365</v>
+      </c>
+      <c r="O37">
+        <v>1.962384204999999</v>
+      </c>
+      <c r="P37">
+        <v>9.581052295000001</v>
+      </c>
+      <c r="Q37">
+        <v>17.981052295</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1433605338711015</v>
+      </c>
+      <c r="T37">
+        <v>1.767945304453542</v>
+      </c>
+      <c r="U37">
+        <v>0.0457</v>
+      </c>
+      <c r="V37">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W37">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>16.25772324464503</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1063286581167715</v>
+      </c>
+      <c r="C38">
+        <v>30.62150552212687</v>
+      </c>
+      <c r="D38">
+        <v>26.14950552212687</v>
+      </c>
+      <c r="E38">
+        <v>9.227999999999998</v>
+      </c>
+      <c r="F38">
+        <v>17.028</v>
+      </c>
+      <c r="G38">
+        <v>21.5</v>
+      </c>
+      <c r="H38">
+        <v>39.5</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>20.7</v>
+      </c>
+      <c r="K38">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L38">
+        <v>12.3</v>
+      </c>
+      <c r="M38">
+        <v>0.7781796</v>
+      </c>
+      <c r="N38">
+        <v>11.5218204</v>
+      </c>
+      <c r="O38">
+        <v>1.958709467999999</v>
+      </c>
+      <c r="P38">
+        <v>9.563110932000001</v>
+      </c>
+      <c r="Q38">
+        <v>17.963110932</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1448023408074554</v>
+      </c>
+      <c r="T38">
+        <v>1.79232386975618</v>
+      </c>
+      <c r="U38">
+        <v>0.0457</v>
+      </c>
+      <c r="V38">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W38">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>15.80611982118267</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.106197119217327</v>
+      </c>
+      <c r="C39">
+        <v>30.16524589820232</v>
+      </c>
+      <c r="D39">
+        <v>26.16624589820232</v>
+      </c>
+      <c r="E39">
+        <v>9.700999999999997</v>
+      </c>
+      <c r="F39">
+        <v>17.501</v>
+      </c>
+      <c r="G39">
+        <v>21.5</v>
+      </c>
+      <c r="H39">
+        <v>39.5</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>20.7</v>
+      </c>
+      <c r="K39">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L39">
+        <v>12.3</v>
+      </c>
+      <c r="M39">
+        <v>0.7997957</v>
+      </c>
+      <c r="N39">
+        <v>11.5002043</v>
+      </c>
+      <c r="O39">
+        <v>1.955034730999999</v>
+      </c>
+      <c r="P39">
+        <v>9.545169569</v>
+      </c>
+      <c r="Q39">
+        <v>17.945169569</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1462899193925825</v>
+      </c>
+      <c r="T39">
+        <v>1.81747635776684</v>
+      </c>
+      <c r="U39">
+        <v>0.0457</v>
+      </c>
+      <c r="V39">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W39">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>15.37892739358314</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1060655803178824</v>
+      </c>
+      <c r="C40">
+        <v>29.70900772169746</v>
+      </c>
+      <c r="D40">
+        <v>26.18300772169747</v>
+      </c>
+      <c r="E40">
+        <v>10.174</v>
+      </c>
+      <c r="F40">
+        <v>17.974</v>
+      </c>
+      <c r="G40">
+        <v>21.5</v>
+      </c>
+      <c r="H40">
+        <v>39.5</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>20.7</v>
+      </c>
+      <c r="K40">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L40">
+        <v>12.3</v>
+      </c>
+      <c r="M40">
+        <v>0.8214118000000001</v>
+      </c>
+      <c r="N40">
+        <v>11.4785882</v>
+      </c>
+      <c r="O40">
+        <v>1.951359993999999</v>
+      </c>
+      <c r="P40">
+        <v>9.527228206000002</v>
+      </c>
+      <c r="Q40">
+        <v>17.927228206</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1478254843836813</v>
+      </c>
+      <c r="T40">
+        <v>1.843440216358488</v>
+      </c>
+      <c r="U40">
+        <v>0.0457</v>
+      </c>
+      <c r="V40">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W40">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>14.97421877796253</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1059340414184379</v>
+      </c>
+      <c r="C41">
+        <v>29.25279103385573</v>
+      </c>
+      <c r="D41">
+        <v>26.19979103385573</v>
+      </c>
+      <c r="E41">
+        <v>10.647</v>
+      </c>
+      <c r="F41">
+        <v>18.447</v>
+      </c>
+      <c r="G41">
+        <v>21.5</v>
+      </c>
+      <c r="H41">
+        <v>39.5</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>20.7</v>
+      </c>
+      <c r="K41">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L41">
+        <v>12.3</v>
+      </c>
+      <c r="M41">
+        <v>0.8430279000000001</v>
+      </c>
+      <c r="N41">
+        <v>11.4569721</v>
+      </c>
+      <c r="O41">
+        <v>1.947685256999999</v>
+      </c>
+      <c r="P41">
+        <v>9.509286843000002</v>
+      </c>
+      <c r="Q41">
+        <v>17.909286843</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.149411395767931</v>
+      </c>
+      <c r="T41">
+        <v>1.870255349002321</v>
+      </c>
+      <c r="U41">
+        <v>0.0457</v>
+      </c>
+      <c r="V41">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W41">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>14.59026445032246</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1058025025189934</v>
+      </c>
+      <c r="C42">
+        <v>28.79659587602632</v>
+      </c>
+      <c r="D42">
+        <v>26.21659587602631</v>
+      </c>
+      <c r="E42">
+        <v>11.12</v>
+      </c>
+      <c r="F42">
+        <v>18.92</v>
+      </c>
+      <c r="G42">
+        <v>21.5</v>
+      </c>
+      <c r="H42">
+        <v>39.5</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>20.7</v>
+      </c>
+      <c r="K42">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L42">
+        <v>12.3</v>
+      </c>
+      <c r="M42">
+        <v>0.864644</v>
+      </c>
+      <c r="N42">
+        <v>11.435356</v>
+      </c>
+      <c r="O42">
+        <v>1.944010519999999</v>
+      </c>
+      <c r="P42">
+        <v>9.491345480000001</v>
+      </c>
+      <c r="Q42">
+        <v>17.89134548</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.151050170864989</v>
+      </c>
+      <c r="T42">
+        <v>1.897964319400949</v>
+      </c>
+      <c r="U42">
+        <v>0.0457</v>
+      </c>
+      <c r="V42">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W42">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>14.2255078390644</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1056709636195489</v>
+      </c>
+      <c r="C43">
+        <v>28.3404222896646</v>
+      </c>
+      <c r="D43">
+        <v>26.2334222896646</v>
+      </c>
+      <c r="E43">
+        <v>11.593</v>
+      </c>
+      <c r="F43">
+        <v>19.393</v>
+      </c>
+      <c r="G43">
+        <v>21.5</v>
+      </c>
+      <c r="H43">
+        <v>39.5</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>20.7</v>
+      </c>
+      <c r="K43">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L43">
+        <v>12.3</v>
+      </c>
+      <c r="M43">
+        <v>0.8862601000000001</v>
+      </c>
+      <c r="N43">
+        <v>11.4137399</v>
+      </c>
+      <c r="O43">
+        <v>1.940335782999999</v>
+      </c>
+      <c r="P43">
+        <v>9.473404117000001</v>
+      </c>
+      <c r="Q43">
+        <v>17.873404117</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1527444976602523</v>
+      </c>
+      <c r="T43">
+        <v>1.926612576931734</v>
+      </c>
+      <c r="U43">
+        <v>0.0457</v>
+      </c>
+      <c r="V43">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W43">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>13.87854423323356</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1055394247201044</v>
+      </c>
+      <c r="C44">
+        <v>27.88427031633243</v>
+      </c>
+      <c r="D44">
+        <v>26.25027031633244</v>
+      </c>
+      <c r="E44">
+        <v>12.066</v>
+      </c>
+      <c r="F44">
+        <v>19.866</v>
+      </c>
+      <c r="G44">
+        <v>21.5</v>
+      </c>
+      <c r="H44">
+        <v>39.5</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>20.7</v>
+      </c>
+      <c r="K44">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L44">
+        <v>12.3</v>
+      </c>
+      <c r="M44">
+        <v>0.9078762</v>
+      </c>
+      <c r="N44">
+        <v>11.3921238</v>
+      </c>
+      <c r="O44">
+        <v>1.936661045999999</v>
+      </c>
+      <c r="P44">
+        <v>9.455462754000001</v>
+      </c>
+      <c r="Q44">
+        <v>17.855462754</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1544972495174213</v>
+      </c>
+      <c r="T44">
+        <v>1.956248705411856</v>
+      </c>
+      <c r="U44">
+        <v>0.0457</v>
+      </c>
+      <c r="V44">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W44">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>13.54810270387086</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1054078858206598</v>
+      </c>
+      <c r="C45">
+        <v>27.42813999769854</v>
+      </c>
+      <c r="D45">
+        <v>26.26713999769854</v>
+      </c>
+      <c r="E45">
+        <v>12.539</v>
+      </c>
+      <c r="F45">
+        <v>20.339</v>
+      </c>
+      <c r="G45">
+        <v>21.5</v>
+      </c>
+      <c r="H45">
+        <v>39.5</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>20.7</v>
+      </c>
+      <c r="K45">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L45">
+        <v>12.3</v>
+      </c>
+      <c r="M45">
+        <v>0.9294923</v>
+      </c>
+      <c r="N45">
+        <v>11.3705077</v>
+      </c>
+      <c r="O45">
+        <v>1.932986308999999</v>
+      </c>
+      <c r="P45">
+        <v>9.437521391000001</v>
+      </c>
+      <c r="Q45">
+        <v>17.837521391</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1563115014397541</v>
+      </c>
+      <c r="T45">
+        <v>1.986924698049175</v>
+      </c>
+      <c r="U45">
+        <v>0.0457</v>
+      </c>
+      <c r="V45">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W45">
+        <v>0.03793100000000001</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>13.23303054796689</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1058606669212153</v>
+      </c>
+      <c r="C46">
+        <v>26.89716238507212</v>
+      </c>
+      <c r="D46">
+        <v>26.20916238507212</v>
+      </c>
+      <c r="E46">
+        <v>13.012</v>
+      </c>
+      <c r="F46">
+        <v>20.812</v>
+      </c>
+      <c r="G46">
+        <v>21.5</v>
+      </c>
+      <c r="H46">
+        <v>39.5</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>20.7</v>
+      </c>
+      <c r="K46">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L46">
+        <v>12.3</v>
+      </c>
+      <c r="M46">
+        <v>0.9844075999999999</v>
+      </c>
+      <c r="N46">
+        <v>11.3155924</v>
+      </c>
+      <c r="O46">
+        <v>1.923650707999999</v>
+      </c>
+      <c r="P46">
+        <v>9.391941692000001</v>
+      </c>
+      <c r="Q46">
+        <v>17.791941692</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1581905480735988</v>
+      </c>
+      <c r="T46">
+        <v>2.018696261852113</v>
+      </c>
+      <c r="U46">
+        <v>0.0473</v>
+      </c>
+      <c r="V46">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W46">
+        <v>0.039259</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>12.49482429839022</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1057424080217708</v>
+      </c>
+      <c r="C47">
+        <v>26.4392804658904</v>
+      </c>
+      <c r="D47">
+        <v>26.2242804658904</v>
+      </c>
+      <c r="E47">
+        <v>13.485</v>
+      </c>
+      <c r="F47">
+        <v>21.285</v>
+      </c>
+      <c r="G47">
+        <v>21.5</v>
+      </c>
+      <c r="H47">
+        <v>39.5</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>20.7</v>
+      </c>
+      <c r="K47">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L47">
+        <v>12.3</v>
+      </c>
+      <c r="M47">
+        <v>1.0067805</v>
+      </c>
+      <c r="N47">
+        <v>11.2932195</v>
+      </c>
+      <c r="O47">
+        <v>1.919847314999999</v>
+      </c>
+      <c r="P47">
+        <v>9.373372185000001</v>
+      </c>
+      <c r="Q47">
+        <v>17.773372185</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1601379236759469</v>
+      </c>
+      <c r="T47">
+        <v>2.051623155247885</v>
+      </c>
+      <c r="U47">
+        <v>0.0473</v>
+      </c>
+      <c r="V47">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W47">
+        <v>0.039259</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>12.21716153620377</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1056241491223263</v>
+      </c>
+      <c r="C48">
+        <v>25.98141599772655</v>
+      </c>
+      <c r="D48">
+        <v>26.23941599772655</v>
+      </c>
+      <c r="E48">
+        <v>13.958</v>
+      </c>
+      <c r="F48">
+        <v>21.758</v>
+      </c>
+      <c r="G48">
+        <v>21.5</v>
+      </c>
+      <c r="H48">
+        <v>39.5</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>20.7</v>
+      </c>
+      <c r="K48">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L48">
+        <v>12.3</v>
+      </c>
+      <c r="M48">
+        <v>1.0291534</v>
+      </c>
+      <c r="N48">
+        <v>11.2708466</v>
+      </c>
+      <c r="O48">
+        <v>1.916043921999999</v>
+      </c>
+      <c r="P48">
+        <v>9.354802678000002</v>
+      </c>
+      <c r="Q48">
+        <v>17.754802678</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1621574243006043</v>
+      </c>
+      <c r="T48">
+        <v>2.085769563213871</v>
+      </c>
+      <c r="U48">
+        <v>0.0473</v>
+      </c>
+      <c r="V48">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W48">
+        <v>0.039259</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>11.95157106802543</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1055058902228818</v>
+      </c>
+      <c r="C49">
+        <v>25.52356901081397</v>
+      </c>
+      <c r="D49">
+        <v>26.25456901081396</v>
+      </c>
+      <c r="E49">
+        <v>14.431</v>
+      </c>
+      <c r="F49">
+        <v>22.231</v>
+      </c>
+      <c r="G49">
+        <v>21.5</v>
+      </c>
+      <c r="H49">
+        <v>39.5</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>20.7</v>
+      </c>
+      <c r="K49">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L49">
+        <v>12.3</v>
+      </c>
+      <c r="M49">
+        <v>1.0515263</v>
+      </c>
+      <c r="N49">
+        <v>11.2484737</v>
+      </c>
+      <c r="O49">
+        <v>1.912240528999999</v>
+      </c>
+      <c r="P49">
+        <v>9.336233171</v>
+      </c>
+      <c r="Q49">
+        <v>17.736233171</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1642531324960034</v>
+      </c>
+      <c r="T49">
+        <v>2.121204514876686</v>
+      </c>
+      <c r="U49">
+        <v>0.0473</v>
+      </c>
+      <c r="V49">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W49">
+        <v>0.039259</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>11.69728232189722</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1053876313234373</v>
+      </c>
+      <c r="C50">
+        <v>25.0657395354559</v>
+      </c>
+      <c r="D50">
+        <v>26.2697395354559</v>
+      </c>
+      <c r="E50">
+        <v>14.904</v>
+      </c>
+      <c r="F50">
+        <v>22.704</v>
+      </c>
+      <c r="G50">
+        <v>21.5</v>
+      </c>
+      <c r="H50">
+        <v>39.5</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>20.7</v>
+      </c>
+      <c r="K50">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L50">
+        <v>12.3</v>
+      </c>
+      <c r="M50">
+        <v>1.0738992</v>
+      </c>
+      <c r="N50">
+        <v>11.2261008</v>
+      </c>
+      <c r="O50">
+        <v>1.908437135999999</v>
+      </c>
+      <c r="P50">
+        <v>9.317663664000001</v>
+      </c>
+      <c r="Q50">
+        <v>17.717663664</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.166429444852764</v>
+      </c>
+      <c r="T50">
+        <v>2.158002349295764</v>
+      </c>
+      <c r="U50">
+        <v>0.0473</v>
+      </c>
+      <c r="V50">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W50">
+        <v>0.039259</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>11.45358894019104</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1052693724239927</v>
+      </c>
+      <c r="C51">
+        <v>24.60792760202572</v>
+      </c>
+      <c r="D51">
+        <v>26.28492760202572</v>
+      </c>
+      <c r="E51">
+        <v>15.377</v>
+      </c>
+      <c r="F51">
+        <v>23.177</v>
+      </c>
+      <c r="G51">
+        <v>21.5</v>
+      </c>
+      <c r="H51">
+        <v>39.5</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>20.7</v>
+      </c>
+      <c r="K51">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L51">
+        <v>12.3</v>
+      </c>
+      <c r="M51">
+        <v>1.0962721</v>
+      </c>
+      <c r="N51">
+        <v>11.2037279</v>
+      </c>
+      <c r="O51">
+        <v>1.904633742999999</v>
+      </c>
+      <c r="P51">
+        <v>9.299094157000001</v>
+      </c>
+      <c r="Q51">
+        <v>17.699094157</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1686911027921426</v>
+      </c>
+      <c r="T51">
+        <v>2.196243236045001</v>
+      </c>
+      <c r="U51">
+        <v>0.0473</v>
+      </c>
+      <c r="V51">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W51">
+        <v>0.039259</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>11.21984222712591</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1051511135245482</v>
+      </c>
+      <c r="C52">
+        <v>24.15013324096705</v>
+      </c>
+      <c r="D52">
+        <v>26.30013324096705</v>
+      </c>
+      <c r="E52">
+        <v>15.85</v>
+      </c>
+      <c r="F52">
+        <v>23.65</v>
+      </c>
+      <c r="G52">
+        <v>21.5</v>
+      </c>
+      <c r="H52">
+        <v>39.5</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>20.7</v>
+      </c>
+      <c r="K52">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L52">
+        <v>12.3</v>
+      </c>
+      <c r="M52">
+        <v>1.118645</v>
+      </c>
+      <c r="N52">
+        <v>11.181355</v>
+      </c>
+      <c r="O52">
+        <v>1.900830349999999</v>
+      </c>
+      <c r="P52">
+        <v>9.28052465</v>
+      </c>
+      <c r="Q52">
+        <v>17.68052465</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1710432270490965</v>
+      </c>
+      <c r="T52">
+        <v>2.236013758264208</v>
+      </c>
+      <c r="U52">
+        <v>0.0473</v>
+      </c>
+      <c r="V52">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W52">
+        <v>0.039259</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>10.99544538258339</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1050328546251037</v>
+      </c>
+      <c r="C53">
+        <v>23.692356482794</v>
+      </c>
+      <c r="D53">
+        <v>26.315356482794</v>
+      </c>
+      <c r="E53">
+        <v>16.323</v>
+      </c>
+      <c r="F53">
+        <v>24.123</v>
+      </c>
+      <c r="G53">
+        <v>21.5</v>
+      </c>
+      <c r="H53">
+        <v>39.5</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>20.7</v>
+      </c>
+      <c r="K53">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L53">
+        <v>12.3</v>
+      </c>
+      <c r="M53">
+        <v>1.1410179</v>
+      </c>
+      <c r="N53">
+        <v>11.1589821</v>
+      </c>
+      <c r="O53">
+        <v>1.897026956999999</v>
+      </c>
+      <c r="P53">
+        <v>9.261955143000002</v>
+      </c>
+      <c r="Q53">
+        <v>17.661955143</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1734913563777627</v>
+      </c>
+      <c r="T53">
+        <v>2.277407567104607</v>
+      </c>
+      <c r="U53">
+        <v>0.0473</v>
+      </c>
+      <c r="V53">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W53">
+        <v>0.039259</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>10.77984841429745</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1049145957256592</v>
+      </c>
+      <c r="C54">
+        <v>23.2345973580914</v>
+      </c>
+      <c r="D54">
+        <v>26.3305973580914</v>
+      </c>
+      <c r="E54">
+        <v>16.796</v>
+      </c>
+      <c r="F54">
+        <v>24.596</v>
+      </c>
+      <c r="G54">
+        <v>21.5</v>
+      </c>
+      <c r="H54">
+        <v>39.5</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>20.7</v>
+      </c>
+      <c r="K54">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L54">
+        <v>12.3</v>
+      </c>
+      <c r="M54">
+        <v>1.1633908</v>
+      </c>
+      <c r="N54">
+        <v>11.1366092</v>
+      </c>
+      <c r="O54">
+        <v>1.893223563999999</v>
+      </c>
+      <c r="P54">
+        <v>9.243385636000001</v>
+      </c>
+      <c r="Q54">
+        <v>17.643385636</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1760414910951233</v>
+      </c>
+      <c r="T54">
+        <v>2.320526117980023</v>
+      </c>
+      <c r="U54">
+        <v>0.0473</v>
+      </c>
+      <c r="V54">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W54">
+        <v>0.039259</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>10.57254363709942</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1047963368262147</v>
+      </c>
+      <c r="C55">
+        <v>22.77685589751494</v>
+      </c>
+      <c r="D55">
+        <v>26.34585589751494</v>
+      </c>
+      <c r="E55">
+        <v>17.269</v>
+      </c>
+      <c r="F55">
+        <v>25.069</v>
+      </c>
+      <c r="G55">
+        <v>21.5</v>
+      </c>
+      <c r="H55">
+        <v>39.5</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>20.7</v>
+      </c>
+      <c r="K55">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L55">
+        <v>12.3</v>
+      </c>
+      <c r="M55">
+        <v>1.1857637</v>
+      </c>
+      <c r="N55">
+        <v>11.1142363</v>
+      </c>
+      <c r="O55">
+        <v>1.889420170999999</v>
+      </c>
+      <c r="P55">
+        <v>9.224816129000001</v>
+      </c>
+      <c r="Q55">
+        <v>17.624816129</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1787001421834355</v>
+      </c>
+      <c r="T55">
+        <v>2.365479500807584</v>
+      </c>
+      <c r="U55">
+        <v>0.0473</v>
+      </c>
+      <c r="V55">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W55">
+        <v>0.039259</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>10.37306168168245</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1063812379267702</v>
+      </c>
+      <c r="C56">
+        <v>22.10081991223642</v>
+      </c>
+      <c r="D56">
+        <v>26.14281991223642</v>
+      </c>
+      <c r="E56">
+        <v>17.742</v>
+      </c>
+      <c r="F56">
+        <v>25.542</v>
+      </c>
+      <c r="G56">
+        <v>21.5</v>
+      </c>
+      <c r="H56">
+        <v>39.5</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>20.7</v>
+      </c>
+      <c r="K56">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L56">
+        <v>12.3</v>
+      </c>
+      <c r="M56">
+        <v>1.3051962</v>
+      </c>
+      <c r="N56">
+        <v>10.9948038</v>
+      </c>
+      <c r="O56">
+        <v>1.869116645999999</v>
+      </c>
+      <c r="P56">
+        <v>9.125687154000001</v>
+      </c>
+      <c r="Q56">
+        <v>17.525687154</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1814743867973264</v>
+      </c>
+      <c r="T56">
+        <v>2.412387378540691</v>
+      </c>
+      <c r="U56">
+        <v>0.0511</v>
+      </c>
+      <c r="V56">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W56">
+        <v>0.04241300000000001</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>9.423870526132392</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1062945190273257</v>
+      </c>
+      <c r="C57">
+        <v>21.63884819504245</v>
+      </c>
+      <c r="D57">
+        <v>26.15384819504245</v>
+      </c>
+      <c r="E57">
+        <v>18.215</v>
+      </c>
+      <c r="F57">
+        <v>26.015</v>
+      </c>
+      <c r="G57">
+        <v>21.5</v>
+      </c>
+      <c r="H57">
+        <v>39.5</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>20.7</v>
+      </c>
+      <c r="K57">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L57">
+        <v>12.3</v>
+      </c>
+      <c r="M57">
+        <v>1.3293665</v>
+      </c>
+      <c r="N57">
+        <v>10.9706335</v>
+      </c>
+      <c r="O57">
+        <v>1.865007694999999</v>
+      </c>
+      <c r="P57">
+        <v>9.105625805000001</v>
+      </c>
+      <c r="Q57">
+        <v>17.505625805</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1843719311718348</v>
+      </c>
+      <c r="T57">
+        <v>2.461380050839715</v>
+      </c>
+      <c r="U57">
+        <v>0.0511</v>
+      </c>
+      <c r="V57">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W57">
+        <v>0.04241300000000001</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>9.252527425657258</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1062078001278811</v>
+      </c>
+      <c r="C58">
+        <v>21.17688578628193</v>
+      </c>
+      <c r="D58">
+        <v>26.16488578628193</v>
+      </c>
+      <c r="E58">
+        <v>18.688</v>
+      </c>
+      <c r="F58">
+        <v>26.488</v>
+      </c>
+      <c r="G58">
+        <v>21.5</v>
+      </c>
+      <c r="H58">
+        <v>39.5</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>20.7</v>
+      </c>
+      <c r="K58">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L58">
+        <v>12.3</v>
+      </c>
+      <c r="M58">
+        <v>1.3535368</v>
+      </c>
+      <c r="N58">
+        <v>10.9464632</v>
+      </c>
+      <c r="O58">
+        <v>1.860898743999999</v>
+      </c>
+      <c r="P58">
+        <v>9.085564456</v>
+      </c>
+      <c r="Q58">
+        <v>17.485564456</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1874011821088208</v>
+      </c>
+      <c r="T58">
+        <v>2.512599662788693</v>
+      </c>
+      <c r="U58">
+        <v>0.0511</v>
+      </c>
+      <c r="V58">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W58">
+        <v>0.04241300000000001</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>9.087303721627666</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1061210812284366</v>
+      </c>
+      <c r="C59">
+        <v>20.71493269774502</v>
+      </c>
+      <c r="D59">
+        <v>26.17593269774502</v>
+      </c>
+      <c r="E59">
+        <v>19.161</v>
+      </c>
+      <c r="F59">
+        <v>26.961</v>
+      </c>
+      <c r="G59">
+        <v>21.5</v>
+      </c>
+      <c r="H59">
+        <v>39.5</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>20.7</v>
+      </c>
+      <c r="K59">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L59">
+        <v>12.3</v>
+      </c>
+      <c r="M59">
+        <v>1.3777071</v>
+      </c>
+      <c r="N59">
+        <v>10.9222929</v>
+      </c>
+      <c r="O59">
+        <v>1.856789792999999</v>
+      </c>
+      <c r="P59">
+        <v>9.065503107000001</v>
+      </c>
+      <c r="Q59">
+        <v>17.465503107</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1905713284382247</v>
+      </c>
+      <c r="T59">
+        <v>2.566201582270183</v>
+      </c>
+      <c r="U59">
+        <v>0.0511</v>
+      </c>
+      <c r="V59">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W59">
+        <v>0.04241300000000001</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>8.927877340546477</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1060343623289921</v>
+      </c>
+      <c r="C60">
+        <v>20.25298894124182</v>
+      </c>
+      <c r="D60">
+        <v>26.18698894124182</v>
+      </c>
+      <c r="E60">
+        <v>19.634</v>
+      </c>
+      <c r="F60">
+        <v>27.434</v>
+      </c>
+      <c r="G60">
+        <v>21.5</v>
+      </c>
+      <c r="H60">
+        <v>39.5</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>20.7</v>
+      </c>
+      <c r="K60">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L60">
+        <v>12.3</v>
+      </c>
+      <c r="M60">
+        <v>1.4018774</v>
+      </c>
+      <c r="N60">
+        <v>10.8981226</v>
+      </c>
+      <c r="O60">
+        <v>1.852680841999999</v>
+      </c>
+      <c r="P60">
+        <v>9.045441758000001</v>
+      </c>
+      <c r="Q60">
+        <v>17.445441758</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1938924341166479</v>
+      </c>
+      <c r="T60">
+        <v>2.622355974107933</v>
+      </c>
+      <c r="U60">
+        <v>0.0511</v>
+      </c>
+      <c r="V60">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W60">
+        <v>0.04241300000000001</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>8.773948420881885</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1059476434295476</v>
+      </c>
+      <c r="C61">
+        <v>19.79105452860237</v>
+      </c>
+      <c r="D61">
+        <v>26.19805452860236</v>
+      </c>
+      <c r="E61">
+        <v>20.107</v>
+      </c>
+      <c r="F61">
+        <v>27.907</v>
+      </c>
+      <c r="G61">
+        <v>21.5</v>
+      </c>
+      <c r="H61">
+        <v>39.5</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>20.7</v>
+      </c>
+      <c r="K61">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L61">
+        <v>12.3</v>
+      </c>
+      <c r="M61">
+        <v>1.4260477</v>
+      </c>
+      <c r="N61">
+        <v>10.8739523</v>
+      </c>
+      <c r="O61">
+        <v>1.848571890999999</v>
+      </c>
+      <c r="P61">
+        <v>9.025380409000002</v>
+      </c>
+      <c r="Q61">
+        <v>17.425380409</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1973755449501161</v>
+      </c>
+      <c r="T61">
+        <v>2.681249604571915</v>
+      </c>
+      <c r="U61">
+        <v>0.0511</v>
+      </c>
+      <c r="V61">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W61">
+        <v>0.04241300000000001</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>8.625237430697446</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1058609245301031</v>
+      </c>
+      <c r="C62">
+        <v>19.3291294716767</v>
+      </c>
+      <c r="D62">
+        <v>26.2091294716767</v>
+      </c>
+      <c r="E62">
+        <v>20.58</v>
+      </c>
+      <c r="F62">
+        <v>28.38</v>
+      </c>
+      <c r="G62">
+        <v>21.5</v>
+      </c>
+      <c r="H62">
+        <v>39.5</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>20.7</v>
+      </c>
+      <c r="K62">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L62">
+        <v>12.3</v>
+      </c>
+      <c r="M62">
+        <v>1.450218</v>
+      </c>
+      <c r="N62">
+        <v>10.849782</v>
+      </c>
+      <c r="O62">
+        <v>1.844462939999999</v>
+      </c>
+      <c r="P62">
+        <v>9.005319060000001</v>
+      </c>
+      <c r="Q62">
+        <v>17.40531906</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2010328113252577</v>
+      </c>
+      <c r="T62">
+        <v>2.743087916559097</v>
+      </c>
+      <c r="U62">
+        <v>0.0511</v>
+      </c>
+      <c r="V62">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W62">
+        <v>0.04241300000000001</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>8.481483473519155</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1057742056306586</v>
+      </c>
+      <c r="C63">
+        <v>18.86721378233494</v>
+      </c>
+      <c r="D63">
+        <v>26.22021378233493</v>
+      </c>
+      <c r="E63">
+        <v>21.053</v>
+      </c>
+      <c r="F63">
+        <v>28.853</v>
+      </c>
+      <c r="G63">
+        <v>21.5</v>
+      </c>
+      <c r="H63">
+        <v>39.5</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>20.7</v>
+      </c>
+      <c r="K63">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L63">
+        <v>12.3</v>
+      </c>
+      <c r="M63">
+        <v>1.4743883</v>
+      </c>
+      <c r="N63">
+        <v>10.8256117</v>
+      </c>
+      <c r="O63">
+        <v>1.840353988999999</v>
+      </c>
+      <c r="P63">
+        <v>8.985257711000003</v>
+      </c>
+      <c r="Q63">
+        <v>17.385257711</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2048776298222015</v>
+      </c>
+      <c r="T63">
+        <v>2.808097424032801</v>
+      </c>
+      <c r="U63">
+        <v>0.0511</v>
+      </c>
+      <c r="V63">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W63">
+        <v>0.04241300000000001</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>8.342442760838512</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.105687486731214</v>
+      </c>
+      <c r="C64">
+        <v>18.40530747246725</v>
+      </c>
+      <c r="D64">
+        <v>26.23130747246725</v>
+      </c>
+      <c r="E64">
+        <v>21.526</v>
+      </c>
+      <c r="F64">
+        <v>29.326</v>
+      </c>
+      <c r="G64">
+        <v>21.5</v>
+      </c>
+      <c r="H64">
+        <v>39.5</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>20.7</v>
+      </c>
+      <c r="K64">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L64">
+        <v>12.3</v>
+      </c>
+      <c r="M64">
+        <v>1.4985586</v>
+      </c>
+      <c r="N64">
+        <v>10.8014414</v>
+      </c>
+      <c r="O64">
+        <v>1.836245037999999</v>
+      </c>
+      <c r="P64">
+        <v>8.965196362000002</v>
+      </c>
+      <c r="Q64">
+        <v>17.365196362</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2089248071874053</v>
+      </c>
+      <c r="T64">
+        <v>2.876528484531435</v>
+      </c>
+      <c r="U64">
+        <v>0.0511</v>
+      </c>
+      <c r="V64">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W64">
+        <v>0.04241300000000001</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>8.207887232437894</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1056007678317695</v>
+      </c>
+      <c r="C65">
+        <v>17.94341055398395</v>
+      </c>
+      <c r="D65">
+        <v>26.24241055398395</v>
+      </c>
+      <c r="E65">
+        <v>21.999</v>
+      </c>
+      <c r="F65">
+        <v>29.799</v>
+      </c>
+      <c r="G65">
+        <v>21.5</v>
+      </c>
+      <c r="H65">
+        <v>39.5</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>20.7</v>
+      </c>
+      <c r="K65">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L65">
+        <v>12.3</v>
+      </c>
+      <c r="M65">
+        <v>1.5227289</v>
+      </c>
+      <c r="N65">
+        <v>10.7772711</v>
+      </c>
+      <c r="O65">
+        <v>1.832136086999999</v>
+      </c>
+      <c r="P65">
+        <v>8.945135013000002</v>
+      </c>
+      <c r="Q65">
+        <v>17.345135013</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2131907508966744</v>
+      </c>
+      <c r="T65">
+        <v>2.948658521273241</v>
+      </c>
+      <c r="U65">
+        <v>0.0511</v>
+      </c>
+      <c r="V65">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W65">
+        <v>0.04241300000000001</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>8.077603308113481</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.105514048932325</v>
+      </c>
+      <c r="C66">
+        <v>17.48152303881556</v>
+      </c>
+      <c r="D66">
+        <v>26.25352303881556</v>
+      </c>
+      <c r="E66">
+        <v>22.472</v>
+      </c>
+      <c r="F66">
+        <v>30.272</v>
+      </c>
+      <c r="G66">
+        <v>21.5</v>
+      </c>
+      <c r="H66">
+        <v>39.5</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>20.7</v>
+      </c>
+      <c r="K66">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L66">
+        <v>12.3</v>
+      </c>
+      <c r="M66">
+        <v>1.5468992</v>
+      </c>
+      <c r="N66">
+        <v>10.7531008</v>
+      </c>
+      <c r="O66">
+        <v>1.828027135999999</v>
+      </c>
+      <c r="P66">
+        <v>8.925073664000001</v>
+      </c>
+      <c r="Q66">
+        <v>17.325073664</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2176936914786806</v>
+      </c>
+      <c r="T66">
+        <v>3.024795782278479</v>
+      </c>
+      <c r="U66">
+        <v>0.0511</v>
+      </c>
+      <c r="V66">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W66">
+        <v>0.04241300000000001</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>7.951390756424207</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1054273300328805</v>
+      </c>
+      <c r="C67">
+        <v>17.01964493891276</v>
+      </c>
+      <c r="D67">
+        <v>26.26464493891275</v>
+      </c>
+      <c r="E67">
+        <v>22.945</v>
+      </c>
+      <c r="F67">
+        <v>30.745</v>
+      </c>
+      <c r="G67">
+        <v>21.5</v>
+      </c>
+      <c r="H67">
+        <v>39.5</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>20.7</v>
+      </c>
+      <c r="K67">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L67">
+        <v>12.3</v>
+      </c>
+      <c r="M67">
+        <v>1.5710695</v>
+      </c>
+      <c r="N67">
+        <v>10.7289305</v>
+      </c>
+      <c r="O67">
+        <v>1.823918184999999</v>
+      </c>
+      <c r="P67">
+        <v>8.905012315</v>
+      </c>
+      <c r="Q67">
+        <v>17.305012315</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2224539429510871</v>
+      </c>
+      <c r="T67">
+        <v>3.105283743912589</v>
+      </c>
+      <c r="U67">
+        <v>0.0511</v>
+      </c>
+      <c r="V67">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W67">
+        <v>0.04241300000000001</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>7.829061667863835</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.106381431133436</v>
+      </c>
+      <c r="C68">
+        <v>16.42479535199296</v>
+      </c>
+      <c r="D68">
+        <v>26.14279535199296</v>
+      </c>
+      <c r="E68">
+        <v>23.418</v>
+      </c>
+      <c r="F68">
+        <v>31.218</v>
+      </c>
+      <c r="G68">
+        <v>21.5</v>
+      </c>
+      <c r="H68">
+        <v>39.5</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>20.7</v>
+      </c>
+      <c r="K68">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L68">
+        <v>12.3</v>
+      </c>
+      <c r="M68">
+        <v>1.654554</v>
+      </c>
+      <c r="N68">
+        <v>10.645446</v>
+      </c>
+      <c r="O68">
+        <v>1.809725819999999</v>
+      </c>
+      <c r="P68">
+        <v>8.835720180000001</v>
+      </c>
+      <c r="Q68">
+        <v>17.23572018</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2274942092159882</v>
+      </c>
+      <c r="T68">
+        <v>3.190506291525175</v>
+      </c>
+      <c r="U68">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V68">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W68">
+        <v>0.04399000000000001</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>7.434027538539087</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1063104822339915</v>
+      </c>
+      <c r="C69">
+        <v>15.96081741111606</v>
+      </c>
+      <c r="D69">
+        <v>26.15181741111606</v>
+      </c>
+      <c r="E69">
+        <v>23.891</v>
+      </c>
+      <c r="F69">
+        <v>31.691</v>
+      </c>
+      <c r="G69">
+        <v>21.5</v>
+      </c>
+      <c r="H69">
+        <v>39.5</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>20.7</v>
+      </c>
+      <c r="K69">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L69">
+        <v>12.3</v>
+      </c>
+      <c r="M69">
+        <v>1.679623</v>
+      </c>
+      <c r="N69">
+        <v>10.620377</v>
+      </c>
+      <c r="O69">
+        <v>1.805464089999999</v>
+      </c>
+      <c r="P69">
+        <v>8.814912910000002</v>
+      </c>
+      <c r="Q69">
+        <v>17.21491291</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2328399461636105</v>
+      </c>
+      <c r="T69">
+        <v>3.280893842023373</v>
+      </c>
+      <c r="U69">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V69">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W69">
+        <v>0.04399000000000001</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>7.323071903635519</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.106239533334547</v>
+      </c>
+      <c r="C70">
+        <v>15.49684569953868</v>
+      </c>
+      <c r="D70">
+        <v>26.16084569953868</v>
+      </c>
+      <c r="E70">
+        <v>24.364</v>
+      </c>
+      <c r="F70">
+        <v>32.164</v>
+      </c>
+      <c r="G70">
+        <v>21.5</v>
+      </c>
+      <c r="H70">
+        <v>39.5</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>20.7</v>
+      </c>
+      <c r="K70">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L70">
+        <v>12.3</v>
+      </c>
+      <c r="M70">
+        <v>1.704692</v>
+      </c>
+      <c r="N70">
+        <v>10.595308</v>
+      </c>
+      <c r="O70">
+        <v>1.801202359999999</v>
+      </c>
+      <c r="P70">
+        <v>8.794105640000002</v>
+      </c>
+      <c r="Q70">
+        <v>17.19410564</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2385197916704593</v>
+      </c>
+      <c r="T70">
+        <v>3.376930614427708</v>
+      </c>
+      <c r="U70">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V70">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W70">
+        <v>0.04399000000000001</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>7.215379669758525</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1061685844351024</v>
+      </c>
+      <c r="C71">
+        <v>15.03288022371461</v>
+      </c>
+      <c r="D71">
+        <v>26.16988022371461</v>
+      </c>
+      <c r="E71">
+        <v>24.837</v>
+      </c>
+      <c r="F71">
+        <v>32.637</v>
+      </c>
+      <c r="G71">
+        <v>21.5</v>
+      </c>
+      <c r="H71">
+        <v>39.5</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>20.7</v>
+      </c>
+      <c r="K71">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L71">
+        <v>12.3</v>
+      </c>
+      <c r="M71">
+        <v>1.729761</v>
+      </c>
+      <c r="N71">
+        <v>10.570239</v>
+      </c>
+      <c r="O71">
+        <v>1.796940629999999</v>
+      </c>
+      <c r="P71">
+        <v>8.773298370000001</v>
+      </c>
+      <c r="Q71">
+        <v>17.17329837</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2445660788229111</v>
+      </c>
+      <c r="T71">
+        <v>3.479163307632323</v>
+      </c>
+      <c r="U71">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V71">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W71">
+        <v>0.04399000000000001</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>7.110808949906953</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1060976355356579</v>
+      </c>
+      <c r="C72">
+        <v>14.56892099010653</v>
+      </c>
+      <c r="D72">
+        <v>26.17892099010654</v>
+      </c>
+      <c r="E72">
+        <v>25.31</v>
+      </c>
+      <c r="F72">
+        <v>33.11</v>
+      </c>
+      <c r="G72">
+        <v>21.5</v>
+      </c>
+      <c r="H72">
+        <v>39.5</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>20.7</v>
+      </c>
+      <c r="K72">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L72">
+        <v>12.3</v>
+      </c>
+      <c r="M72">
+        <v>1.75483</v>
+      </c>
+      <c r="N72">
+        <v>10.54517</v>
+      </c>
+      <c r="O72">
+        <v>1.792678899999999</v>
+      </c>
+      <c r="P72">
+        <v>8.7524911</v>
+      </c>
+      <c r="Q72">
+        <v>17.1524911</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2510154517855264</v>
+      </c>
+      <c r="T72">
+        <v>3.588211513717245</v>
+      </c>
+      <c r="U72">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V72">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W72">
+        <v>0.04399000000000001</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>7.009225964908282</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1060266866362134</v>
+      </c>
+      <c r="C73">
+        <v>14.10496800518609</v>
+      </c>
+      <c r="D73">
+        <v>26.18796800518609</v>
+      </c>
+      <c r="E73">
+        <v>25.783</v>
+      </c>
+      <c r="F73">
+        <v>33.583</v>
+      </c>
+      <c r="G73">
+        <v>21.5</v>
+      </c>
+      <c r="H73">
+        <v>39.5</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>20.7</v>
+      </c>
+      <c r="K73">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L73">
+        <v>12.3</v>
+      </c>
+      <c r="M73">
+        <v>1.779899</v>
+      </c>
+      <c r="N73">
+        <v>10.520101</v>
+      </c>
+      <c r="O73">
+        <v>1.788417169999999</v>
+      </c>
+      <c r="P73">
+        <v>8.731683830000001</v>
+      </c>
+      <c r="Q73">
+        <v>17.13168383</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2579096090903911</v>
+      </c>
+      <c r="T73">
+        <v>3.704780285739058</v>
+      </c>
+      <c r="U73">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V73">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W73">
+        <v>0.04399000000000001</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>6.910504472444784</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1059557377367689</v>
+      </c>
+      <c r="C74">
+        <v>13.64102127543386</v>
+      </c>
+      <c r="D74">
+        <v>26.19702127543386</v>
+      </c>
+      <c r="E74">
+        <v>26.256</v>
+      </c>
+      <c r="F74">
+        <v>34.056</v>
+      </c>
+      <c r="G74">
+        <v>21.5</v>
+      </c>
+      <c r="H74">
+        <v>39.5</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>20.7</v>
+      </c>
+      <c r="K74">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L74">
+        <v>12.3</v>
+      </c>
+      <c r="M74">
+        <v>1.804968</v>
+      </c>
+      <c r="N74">
+        <v>10.495032</v>
+      </c>
+      <c r="O74">
+        <v>1.784155439999999</v>
+      </c>
+      <c r="P74">
+        <v>8.710876560000001</v>
+      </c>
+      <c r="Q74">
+        <v>17.11087656</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.265296206202746</v>
+      </c>
+      <c r="T74">
+        <v>3.829675398619572</v>
+      </c>
+      <c r="U74">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V74">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W74">
+        <v>0.04399000000000001</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>6.814525243660829</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1058847888373244</v>
+      </c>
+      <c r="C75">
+        <v>13.17708080733938</v>
+      </c>
+      <c r="D75">
+        <v>26.20608080733938</v>
+      </c>
+      <c r="E75">
+        <v>26.729</v>
+      </c>
+      <c r="F75">
+        <v>34.529</v>
+      </c>
+      <c r="G75">
+        <v>21.5</v>
+      </c>
+      <c r="H75">
+        <v>39.5</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>20.7</v>
+      </c>
+      <c r="K75">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L75">
+        <v>12.3</v>
+      </c>
+      <c r="M75">
+        <v>1.830037</v>
+      </c>
+      <c r="N75">
+        <v>10.469963</v>
+      </c>
+      <c r="O75">
+        <v>1.779893709999999</v>
+      </c>
+      <c r="P75">
+        <v>8.69006929</v>
+      </c>
+      <c r="Q75">
+        <v>17.09006929</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2732299586567569</v>
+      </c>
+      <c r="T75">
+        <v>3.963822001343088</v>
+      </c>
+      <c r="U75">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V75">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W75">
+        <v>0.04399000000000001</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>6.721175582788764</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1058138399378798</v>
+      </c>
+      <c r="C76">
+        <v>12.71314660740118</v>
+      </c>
+      <c r="D76">
+        <v>26.21514660740117</v>
+      </c>
+      <c r="E76">
+        <v>27.20199999999999</v>
+      </c>
+      <c r="F76">
+        <v>35.002</v>
+      </c>
+      <c r="G76">
+        <v>21.5</v>
+      </c>
+      <c r="H76">
+        <v>39.5</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>20.7</v>
+      </c>
+      <c r="K76">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L76">
+        <v>12.3</v>
+      </c>
+      <c r="M76">
+        <v>1.855106</v>
+      </c>
+      <c r="N76">
+        <v>10.444894</v>
+      </c>
+      <c r="O76">
+        <v>1.77563198</v>
+      </c>
+      <c r="P76">
+        <v>8.669262020000001</v>
+      </c>
+      <c r="Q76">
+        <v>17.06926202</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2817739997610763</v>
+      </c>
+      <c r="T76">
+        <v>4.108287573506874</v>
+      </c>
+      <c r="U76">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V76">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W76">
+        <v>0.04399000000000001</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>6.630348885724051</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1057428910384353</v>
+      </c>
+      <c r="C77">
+        <v>12.24921868212676</v>
+      </c>
+      <c r="D77">
+        <v>26.22421868212675</v>
+      </c>
+      <c r="E77">
+        <v>27.67499999999999</v>
+      </c>
+      <c r="F77">
+        <v>35.47499999999999</v>
+      </c>
+      <c r="G77">
+        <v>21.5</v>
+      </c>
+      <c r="H77">
+        <v>39.5</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>20.7</v>
+      </c>
+      <c r="K77">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L77">
+        <v>12.3</v>
+      </c>
+      <c r="M77">
+        <v>1.880175</v>
+      </c>
+      <c r="N77">
+        <v>10.419825</v>
+      </c>
+      <c r="O77">
+        <v>1.771370249999999</v>
+      </c>
+      <c r="P77">
+        <v>8.648454750000003</v>
+      </c>
+      <c r="Q77">
+        <v>17.04845475</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2910015641537413</v>
+      </c>
+      <c r="T77">
+        <v>4.264310391443763</v>
+      </c>
+      <c r="U77">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V77">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W77">
+        <v>0.04399000000000001</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>6.541944233914397</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1056719421389908</v>
+      </c>
+      <c r="C78">
+        <v>11.78529703803266</v>
+      </c>
+      <c r="D78">
+        <v>26.23329703803266</v>
+      </c>
+      <c r="E78">
+        <v>28.148</v>
+      </c>
+      <c r="F78">
+        <v>35.948</v>
+      </c>
+      <c r="G78">
+        <v>21.5</v>
+      </c>
+      <c r="H78">
+        <v>39.5</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>20.7</v>
+      </c>
+      <c r="K78">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L78">
+        <v>12.3</v>
+      </c>
+      <c r="M78">
+        <v>1.905244</v>
+      </c>
+      <c r="N78">
+        <v>10.394756</v>
+      </c>
+      <c r="O78">
+        <v>1.767108519999999</v>
+      </c>
+      <c r="P78">
+        <v>8.627647480000002</v>
+      </c>
+      <c r="Q78">
+        <v>17.02764748</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3009980922457951</v>
+      </c>
+      <c r="T78">
+        <v>4.433335110875393</v>
+      </c>
+      <c r="U78">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V78">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W78">
+        <v>0.04399000000000001</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>6.45586602031026</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1056009932395463</v>
+      </c>
+      <c r="C79">
+        <v>11.32138168164445</v>
+      </c>
+      <c r="D79">
+        <v>26.24238168164444</v>
+      </c>
+      <c r="E79">
+        <v>28.621</v>
+      </c>
+      <c r="F79">
+        <v>36.421</v>
+      </c>
+      <c r="G79">
+        <v>21.5</v>
+      </c>
+      <c r="H79">
+        <v>39.5</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>20.7</v>
+      </c>
+      <c r="K79">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L79">
+        <v>12.3</v>
+      </c>
+      <c r="M79">
+        <v>1.930313</v>
+      </c>
+      <c r="N79">
+        <v>10.369687</v>
+      </c>
+      <c r="O79">
+        <v>1.762846789999999</v>
+      </c>
+      <c r="P79">
+        <v>8.606840210000001</v>
+      </c>
+      <c r="Q79">
+        <v>17.00684021</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3118638836502013</v>
+      </c>
+      <c r="T79">
+        <v>4.61705763199673</v>
+      </c>
+      <c r="U79">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V79">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W79">
+        <v>0.04399000000000001</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>6.372023604462075</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1055300443401018</v>
+      </c>
+      <c r="C80">
+        <v>10.8574726194967</v>
+      </c>
+      <c r="D80">
+        <v>26.2514726194967</v>
+      </c>
+      <c r="E80">
+        <v>29.094</v>
+      </c>
+      <c r="F80">
+        <v>36.894</v>
+      </c>
+      <c r="G80">
+        <v>21.5</v>
+      </c>
+      <c r="H80">
+        <v>39.5</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>20.7</v>
+      </c>
+      <c r="K80">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L80">
+        <v>12.3</v>
+      </c>
+      <c r="M80">
+        <v>1.955382</v>
+      </c>
+      <c r="N80">
+        <v>10.344618</v>
+      </c>
+      <c r="O80">
+        <v>1.758585059999999</v>
+      </c>
+      <c r="P80">
+        <v>8.586032940000001</v>
+      </c>
+      <c r="Q80">
+        <v>16.98603294</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.32371747427319</v>
+      </c>
+      <c r="T80">
+        <v>4.817482200492733</v>
+      </c>
+      <c r="U80">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V80">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W80">
+        <v>0.04399000000000001</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>6.290330994148458</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1067704954406573</v>
+      </c>
+      <c r="C81">
+        <v>10.2264313099301</v>
+      </c>
+      <c r="D81">
+        <v>26.0934313099301</v>
+      </c>
+      <c r="E81">
+        <v>29.567</v>
+      </c>
+      <c r="F81">
+        <v>37.367</v>
+      </c>
+      <c r="G81">
+        <v>21.5</v>
+      </c>
+      <c r="H81">
+        <v>39.5</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>20.7</v>
+      </c>
+      <c r="K81">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L81">
+        <v>12.3</v>
+      </c>
+      <c r="M81">
+        <v>2.055185</v>
+      </c>
+      <c r="N81">
+        <v>10.244815</v>
+      </c>
+      <c r="O81">
+        <v>1.741618549999999</v>
+      </c>
+      <c r="P81">
+        <v>8.503196450000001</v>
+      </c>
+      <c r="Q81">
+        <v>16.90319645</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3366999782888442</v>
+      </c>
+      <c r="T81">
+        <v>5.036994823131213</v>
+      </c>
+      <c r="U81">
+        <v>0.055</v>
+      </c>
+      <c r="V81">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W81">
+        <v>0.04565</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>5.984862676596025</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1067161465412128</v>
+      </c>
+      <c r="C82">
+        <v>9.760315832321972</v>
+      </c>
+      <c r="D82">
+        <v>26.10031583232196</v>
+      </c>
+      <c r="E82">
+        <v>30.04</v>
+      </c>
+      <c r="F82">
+        <v>37.84</v>
+      </c>
+      <c r="G82">
+        <v>21.5</v>
+      </c>
+      <c r="H82">
+        <v>39.5</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>20.7</v>
+      </c>
+      <c r="K82">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L82">
+        <v>12.3</v>
+      </c>
+      <c r="M82">
+        <v>2.0812</v>
+      </c>
+      <c r="N82">
+        <v>10.2188</v>
+      </c>
+      <c r="O82">
+        <v>1.737196</v>
+      </c>
+      <c r="P82">
+        <v>8.481604000000003</v>
+      </c>
+      <c r="Q82">
+        <v>16.881604</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3509807327060639</v>
+      </c>
+      <c r="T82">
+        <v>5.278458708033542</v>
+      </c>
+      <c r="U82">
+        <v>0.055</v>
+      </c>
+      <c r="V82">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W82">
+        <v>0.04565</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>5.910051893138575</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1066617976417682</v>
+      </c>
+      <c r="C83">
+        <v>9.294203988513956</v>
+      </c>
+      <c r="D83">
+        <v>26.10720398851396</v>
+      </c>
+      <c r="E83">
+        <v>30.513</v>
+      </c>
+      <c r="F83">
+        <v>38.313</v>
+      </c>
+      <c r="G83">
+        <v>21.5</v>
+      </c>
+      <c r="H83">
+        <v>39.5</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>20.7</v>
+      </c>
+      <c r="K83">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L83">
+        <v>12.3</v>
+      </c>
+      <c r="M83">
+        <v>2.107215</v>
+      </c>
+      <c r="N83">
+        <v>10.192785</v>
+      </c>
+      <c r="O83">
+        <v>1.732773449999999</v>
+      </c>
+      <c r="P83">
+        <v>8.460011550000001</v>
+      </c>
+      <c r="Q83">
+        <v>16.86001155</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3667647244303592</v>
+      </c>
+      <c r="T83">
+        <v>5.54533984397822</v>
+      </c>
+      <c r="U83">
+        <v>0.055</v>
+      </c>
+      <c r="V83">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W83">
+        <v>0.04565</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>5.837088289519579</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1066074487423237</v>
+      </c>
+      <c r="C84">
+        <v>8.828095781383837</v>
+      </c>
+      <c r="D84">
+        <v>26.11409578138384</v>
+      </c>
+      <c r="E84">
+        <v>30.986</v>
+      </c>
+      <c r="F84">
+        <v>38.786</v>
+      </c>
+      <c r="G84">
+        <v>21.5</v>
+      </c>
+      <c r="H84">
+        <v>39.5</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>20.7</v>
+      </c>
+      <c r="K84">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L84">
+        <v>12.3</v>
+      </c>
+      <c r="M84">
+        <v>2.13323</v>
+      </c>
+      <c r="N84">
+        <v>10.16677</v>
+      </c>
+      <c r="O84">
+        <v>1.728350899999999</v>
+      </c>
+      <c r="P84">
+        <v>8.438419100000001</v>
+      </c>
+      <c r="Q84">
+        <v>16.8384191</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3843024930129097</v>
+      </c>
+      <c r="T84">
+        <v>5.841874439472307</v>
+      </c>
+      <c r="U84">
+        <v>0.055</v>
+      </c>
+      <c r="V84">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W84">
+        <v>0.04565</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>5.765904285988852</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.1065530998428792</v>
+      </c>
+      <c r="C85">
+        <v>8.361991213812402</v>
+      </c>
+      <c r="D85">
+        <v>26.12099121381241</v>
+      </c>
+      <c r="E85">
+        <v>31.459</v>
+      </c>
+      <c r="F85">
+        <v>39.259</v>
+      </c>
+      <c r="G85">
+        <v>21.5</v>
+      </c>
+      <c r="H85">
+        <v>39.5</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>20.7</v>
+      </c>
+      <c r="K85">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L85">
+        <v>12.3</v>
+      </c>
+      <c r="M85">
+        <v>2.159245</v>
+      </c>
+      <c r="N85">
+        <v>10.140755</v>
+      </c>
+      <c r="O85">
+        <v>1.723928349999999</v>
+      </c>
+      <c r="P85">
+        <v>8.416826650000001</v>
+      </c>
+      <c r="Q85">
+        <v>16.81682665</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4039035284875249</v>
+      </c>
+      <c r="T85">
+        <v>6.1732954579657</v>
+      </c>
+      <c r="U85">
+        <v>0.055</v>
+      </c>
+      <c r="V85">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W85">
+        <v>0.04565</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>5.696435559651638</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.1064987509434347</v>
+      </c>
+      <c r="C86">
+        <v>7.895890288683503</v>
+      </c>
+      <c r="D86">
+        <v>26.1278902886835</v>
+      </c>
+      <c r="E86">
+        <v>31.932</v>
+      </c>
+      <c r="F86">
+        <v>39.732</v>
+      </c>
+      <c r="G86">
+        <v>21.5</v>
+      </c>
+      <c r="H86">
+        <v>39.5</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>20.7</v>
+      </c>
+      <c r="K86">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L86">
+        <v>12.3</v>
+      </c>
+      <c r="M86">
+        <v>2.18526</v>
+      </c>
+      <c r="N86">
+        <v>10.11474</v>
+      </c>
+      <c r="O86">
+        <v>1.719505799999999</v>
+      </c>
+      <c r="P86">
+        <v>8.395234200000001</v>
+      </c>
+      <c r="Q86">
+        <v>16.7952342</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4259546933964668</v>
+      </c>
+      <c r="T86">
+        <v>6.546144103770762</v>
+      </c>
+      <c r="U86">
+        <v>0.055</v>
+      </c>
+      <c r="V86">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W86">
+        <v>0.04565</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>5.628620850608166</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.1064444020439902</v>
+      </c>
+      <c r="C87">
+        <v>7.429793008884005</v>
+      </c>
+      <c r="D87">
+        <v>26.134793008884</v>
+      </c>
+      <c r="E87">
+        <v>32.405</v>
+      </c>
+      <c r="F87">
+        <v>40.205</v>
+      </c>
+      <c r="G87">
+        <v>21.5</v>
+      </c>
+      <c r="H87">
+        <v>39.5</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>20.7</v>
+      </c>
+      <c r="K87">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L87">
+        <v>12.3</v>
+      </c>
+      <c r="M87">
+        <v>2.211275</v>
+      </c>
+      <c r="N87">
+        <v>10.088725</v>
+      </c>
+      <c r="O87">
+        <v>1.715083249999999</v>
+      </c>
+      <c r="P87">
+        <v>8.373641750000001</v>
+      </c>
+      <c r="Q87">
+        <v>16.77364175</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4509460136266011</v>
+      </c>
+      <c r="T87">
+        <v>6.968705902349836</v>
+      </c>
+      <c r="U87">
+        <v>0.055</v>
+      </c>
+      <c r="V87">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W87">
+        <v>0.04565</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>5.562401781777481</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.1063900531445457</v>
+      </c>
+      <c r="C88">
+        <v>6.963699377303861</v>
+      </c>
+      <c r="D88">
+        <v>26.14169937730386</v>
+      </c>
+      <c r="E88">
+        <v>32.878</v>
+      </c>
+      <c r="F88">
+        <v>40.678</v>
+      </c>
+      <c r="G88">
+        <v>21.5</v>
+      </c>
+      <c r="H88">
+        <v>39.5</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>20.7</v>
+      </c>
+      <c r="K88">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L88">
+        <v>12.3</v>
+      </c>
+      <c r="M88">
+        <v>2.23729</v>
+      </c>
+      <c r="N88">
+        <v>10.06271</v>
+      </c>
+      <c r="O88">
+        <v>1.710660699999999</v>
+      </c>
+      <c r="P88">
+        <v>8.352049300000001</v>
+      </c>
+      <c r="Q88">
+        <v>16.7520493</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4795075224610404</v>
+      </c>
+      <c r="T88">
+        <v>7.451633672154491</v>
+      </c>
+      <c r="U88">
+        <v>0.055</v>
+      </c>
+      <c r="V88">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W88">
+        <v>0.04565</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>5.497722691291697</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.1063357042451012</v>
+      </c>
+      <c r="C89">
+        <v>6.497609396836062</v>
+      </c>
+      <c r="D89">
+        <v>26.14860939683606</v>
+      </c>
+      <c r="E89">
+        <v>33.351</v>
+      </c>
+      <c r="F89">
+        <v>41.151</v>
+      </c>
+      <c r="G89">
+        <v>21.5</v>
+      </c>
+      <c r="H89">
+        <v>39.5</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>20.7</v>
+      </c>
+      <c r="K89">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L89">
+        <v>12.3</v>
+      </c>
+      <c r="M89">
+        <v>2.263305</v>
+      </c>
+      <c r="N89">
+        <v>10.036695</v>
+      </c>
+      <c r="O89">
+        <v>1.70623815</v>
+      </c>
+      <c r="P89">
+        <v>8.330456850000003</v>
+      </c>
+      <c r="Q89">
+        <v>16.73045685</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.5124631095777011</v>
+      </c>
+      <c r="T89">
+        <v>8.008858021929095</v>
+      </c>
+      <c r="U89">
+        <v>0.055</v>
+      </c>
+      <c r="V89">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W89">
+        <v>0.04565</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>5.434530476449265</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.1062813553456566</v>
+      </c>
+      <c r="C90">
+        <v>6.031523070376664</v>
+      </c>
+      <c r="D90">
+        <v>26.15552307037666</v>
+      </c>
+      <c r="E90">
+        <v>33.824</v>
+      </c>
+      <c r="F90">
+        <v>41.624</v>
+      </c>
+      <c r="G90">
+        <v>21.5</v>
+      </c>
+      <c r="H90">
+        <v>39.5</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>20.7</v>
+      </c>
+      <c r="K90">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L90">
+        <v>12.3</v>
+      </c>
+      <c r="M90">
+        <v>2.28932</v>
+      </c>
+      <c r="N90">
+        <v>10.01068</v>
+      </c>
+      <c r="O90">
+        <v>1.701815599999999</v>
+      </c>
+      <c r="P90">
+        <v>8.308864400000001</v>
+      </c>
+      <c r="Q90">
+        <v>16.7088644</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.5509112945471386</v>
+      </c>
+      <c r="T90">
+        <v>8.658953096666133</v>
+      </c>
+      <c r="U90">
+        <v>0.055</v>
+      </c>
+      <c r="V90">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W90">
+        <v>0.04565</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>5.372774448307796</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.1062270064462121</v>
+      </c>
+      <c r="C91">
+        <v>5.565440400824791</v>
+      </c>
+      <c r="D91">
+        <v>26.16244040082479</v>
+      </c>
+      <c r="E91">
+        <v>34.297</v>
+      </c>
+      <c r="F91">
+        <v>42.097</v>
+      </c>
+      <c r="G91">
+        <v>21.5</v>
+      </c>
+      <c r="H91">
+        <v>39.5</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>20.7</v>
+      </c>
+      <c r="K91">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L91">
+        <v>12.3</v>
+      </c>
+      <c r="M91">
+        <v>2.315335</v>
+      </c>
+      <c r="N91">
+        <v>9.984665</v>
+      </c>
+      <c r="O91">
+        <v>1.697393049999999</v>
+      </c>
+      <c r="P91">
+        <v>8.287271950000001</v>
+      </c>
+      <c r="Q91">
+        <v>16.68727195</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5963500586019284</v>
+      </c>
+      <c r="T91">
+        <v>9.427247275900813</v>
+      </c>
+      <c r="U91">
+        <v>0.055</v>
+      </c>
+      <c r="V91">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W91">
+        <v>0.04565</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>5.312406196079617</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.1061726575467676</v>
+      </c>
+      <c r="C92">
+        <v>5.099361391082617</v>
+      </c>
+      <c r="D92">
+        <v>26.16936139108261</v>
+      </c>
+      <c r="E92">
+        <v>34.77</v>
+      </c>
+      <c r="F92">
+        <v>42.57</v>
+      </c>
+      <c r="G92">
+        <v>21.5</v>
+      </c>
+      <c r="H92">
+        <v>39.5</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>20.7</v>
+      </c>
+      <c r="K92">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L92">
+        <v>12.3</v>
+      </c>
+      <c r="M92">
+        <v>2.34135</v>
+      </c>
+      <c r="N92">
+        <v>9.95865</v>
+      </c>
+      <c r="O92">
+        <v>1.692970499999999</v>
+      </c>
+      <c r="P92">
+        <v>8.265679500000001</v>
+      </c>
+      <c r="Q92">
+        <v>16.6656795</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.6508765754676762</v>
+      </c>
+      <c r="T92">
+        <v>10.34920029098243</v>
+      </c>
+      <c r="U92">
+        <v>0.055</v>
+      </c>
+      <c r="V92">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W92">
+        <v>0.04565</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>5.253379460567622</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.1061183086473231</v>
+      </c>
+      <c r="C93">
+        <v>4.633286044055403</v>
+      </c>
+      <c r="D93">
+        <v>26.1762860440554</v>
+      </c>
+      <c r="E93">
+        <v>35.243</v>
+      </c>
+      <c r="F93">
+        <v>43.043</v>
+      </c>
+      <c r="G93">
+        <v>21.5</v>
+      </c>
+      <c r="H93">
+        <v>39.5</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>20.7</v>
+      </c>
+      <c r="K93">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L93">
+        <v>12.3</v>
+      </c>
+      <c r="M93">
+        <v>2.367365</v>
+      </c>
+      <c r="N93">
+        <v>9.932635000000001</v>
+      </c>
+      <c r="O93">
+        <v>1.68854795</v>
+      </c>
+      <c r="P93">
+        <v>8.244087050000001</v>
+      </c>
+      <c r="Q93">
+        <v>16.64408705</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.7175200960813677</v>
+      </c>
+      <c r="T93">
+        <v>11.47603175385996</v>
+      </c>
+      <c r="U93">
+        <v>0.055</v>
+      </c>
+      <c r="V93">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W93">
+        <v>0.04565</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>5.195650015946</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.1060639597478786</v>
+      </c>
+      <c r="C94">
+        <v>4.167214362651485</v>
+      </c>
+      <c r="D94">
+        <v>26.18321436265149</v>
+      </c>
+      <c r="E94">
+        <v>35.716</v>
+      </c>
+      <c r="F94">
+        <v>43.516</v>
+      </c>
+      <c r="G94">
+        <v>21.5</v>
+      </c>
+      <c r="H94">
+        <v>39.5</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>20.7</v>
+      </c>
+      <c r="K94">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L94">
+        <v>12.3</v>
+      </c>
+      <c r="M94">
+        <v>2.39338</v>
+      </c>
+      <c r="N94">
+        <v>9.90662</v>
+      </c>
+      <c r="O94">
+        <v>1.684125399999999</v>
+      </c>
+      <c r="P94">
+        <v>8.222494600000001</v>
+      </c>
+      <c r="Q94">
+        <v>16.6224946</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.8008244968484826</v>
+      </c>
+      <c r="T94">
+        <v>12.88457108245688</v>
+      </c>
+      <c r="U94">
+        <v>0.055</v>
+      </c>
+      <c r="V94">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W94">
+        <v>0.04565</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>5.139175559250933</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.1060096108484341</v>
+      </c>
+      <c r="C95">
+        <v>3.701146349782285</v>
+      </c>
+      <c r="D95">
+        <v>26.19014634978228</v>
+      </c>
+      <c r="E95">
+        <v>36.189</v>
+      </c>
+      <c r="F95">
+        <v>43.989</v>
+      </c>
+      <c r="G95">
+        <v>21.5</v>
+      </c>
+      <c r="H95">
+        <v>39.5</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>20.7</v>
+      </c>
+      <c r="K95">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L95">
+        <v>12.3</v>
+      </c>
+      <c r="M95">
+        <v>2.419395</v>
+      </c>
+      <c r="N95">
+        <v>9.880605000000001</v>
+      </c>
+      <c r="O95">
+        <v>1.67970285</v>
+      </c>
+      <c r="P95">
+        <v>8.200902150000001</v>
+      </c>
+      <c r="Q95">
+        <v>16.60090215</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.90793015497763</v>
+      </c>
+      <c r="T95">
+        <v>14.69555021922434</v>
+      </c>
+      <c r="U95">
+        <v>0.055</v>
+      </c>
+      <c r="V95">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W95">
+        <v>0.04565</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>5.083915607000924</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.1059552619489895</v>
+      </c>
+      <c r="C96">
+        <v>3.235082008362284</v>
+      </c>
+      <c r="D96">
+        <v>26.19708200836228</v>
+      </c>
+      <c r="E96">
+        <v>36.66200000000001</v>
+      </c>
+      <c r="F96">
+        <v>44.462</v>
+      </c>
+      <c r="G96">
+        <v>21.5</v>
+      </c>
+      <c r="H96">
+        <v>39.5</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>20.7</v>
+      </c>
+      <c r="K96">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L96">
+        <v>12.3</v>
+      </c>
+      <c r="M96">
+        <v>2.44541</v>
+      </c>
+      <c r="N96">
+        <v>9.85459</v>
+      </c>
+      <c r="O96">
+        <v>1.675280299999999</v>
+      </c>
+      <c r="P96">
+        <v>8.179309700000001</v>
+      </c>
+      <c r="Q96">
+        <v>16.5793097</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.050737699149827</v>
+      </c>
+      <c r="T96">
+        <v>17.11018906824763</v>
+      </c>
+      <c r="U96">
+        <v>0.055</v>
+      </c>
+      <c r="V96">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W96">
+        <v>0.04565</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>5.029831398415807</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.105900913049545</v>
+      </c>
+      <c r="C97">
+        <v>2.769021341309077</v>
+      </c>
+      <c r="D97">
+        <v>26.20402134130908</v>
+      </c>
+      <c r="E97">
+        <v>37.13500000000001</v>
+      </c>
+      <c r="F97">
+        <v>44.935</v>
+      </c>
+      <c r="G97">
+        <v>21.5</v>
+      </c>
+      <c r="H97">
+        <v>39.5</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>20.7</v>
+      </c>
+      <c r="K97">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L97">
+        <v>12.3</v>
+      </c>
+      <c r="M97">
+        <v>2.471425</v>
+      </c>
+      <c r="N97">
+        <v>9.828575000000001</v>
+      </c>
+      <c r="O97">
+        <v>1.670857749999999</v>
+      </c>
+      <c r="P97">
+        <v>8.157717250000001</v>
+      </c>
+      <c r="Q97">
+        <v>16.55771725</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.250668260990902</v>
+      </c>
+      <c r="T97">
+        <v>20.49068345688023</v>
+      </c>
+      <c r="U97">
+        <v>0.055</v>
+      </c>
+      <c r="V97">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W97">
+        <v>0.04565</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>4.976885804748273</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.1058465641501005</v>
+      </c>
+      <c r="C98">
+        <v>2.302964351543352</v>
+      </c>
+      <c r="D98">
+        <v>26.21096435154335</v>
+      </c>
+      <c r="E98">
+        <v>37.608</v>
+      </c>
+      <c r="F98">
+        <v>45.40799999999999</v>
+      </c>
+      <c r="G98">
+        <v>21.5</v>
+      </c>
+      <c r="H98">
+        <v>39.5</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>20.7</v>
+      </c>
+      <c r="K98">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L98">
+        <v>12.3</v>
+      </c>
+      <c r="M98">
+        <v>2.49744</v>
+      </c>
+      <c r="N98">
+        <v>9.802560000000001</v>
+      </c>
+      <c r="O98">
+        <v>1.6664352</v>
+      </c>
+      <c r="P98">
+        <v>8.136124800000001</v>
+      </c>
+      <c r="Q98">
+        <v>16.5361248</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.550564103752511</v>
+      </c>
+      <c r="T98">
+        <v>25.56142503982907</v>
+      </c>
+      <c r="U98">
+        <v>0.055</v>
+      </c>
+      <c r="V98">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W98">
+        <v>0.04565</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>4.925043244282146</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.105792215250656</v>
+      </c>
+      <c r="C99">
+        <v>1.836911041988856</v>
+      </c>
+      <c r="D99">
+        <v>26.21791104198885</v>
+      </c>
+      <c r="E99">
+        <v>38.081</v>
+      </c>
+      <c r="F99">
+        <v>45.88099999999999</v>
+      </c>
+      <c r="G99">
+        <v>21.5</v>
+      </c>
+      <c r="H99">
+        <v>39.5</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>20.7</v>
+      </c>
+      <c r="K99">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L99">
+        <v>12.3</v>
+      </c>
+      <c r="M99">
+        <v>2.523455</v>
+      </c>
+      <c r="N99">
+        <v>9.776545</v>
+      </c>
+      <c r="O99">
+        <v>1.662012649999999</v>
+      </c>
+      <c r="P99">
+        <v>8.114532350000001</v>
+      </c>
+      <c r="Q99">
+        <v>16.51453235</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.050390508355199</v>
+      </c>
+      <c r="T99">
+        <v>34.01266101141054</v>
+      </c>
+      <c r="U99">
+        <v>0.055</v>
+      </c>
+      <c r="V99">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W99">
+        <v>0.04565</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>4.874269602588515</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.1057378663512115</v>
+      </c>
+      <c r="C100">
+        <v>1.370861415572477</v>
+      </c>
+      <c r="D100">
+        <v>26.22486141557248</v>
+      </c>
+      <c r="E100">
+        <v>38.554</v>
+      </c>
+      <c r="F100">
+        <v>46.354</v>
+      </c>
+      <c r="G100">
+        <v>21.5</v>
+      </c>
+      <c r="H100">
+        <v>39.5</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>20.7</v>
+      </c>
+      <c r="K100">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L100">
+        <v>12.3</v>
+      </c>
+      <c r="M100">
+        <v>2.54947</v>
+      </c>
+      <c r="N100">
+        <v>9.750530000000001</v>
+      </c>
+      <c r="O100">
+        <v>1.6575901</v>
+      </c>
+      <c r="P100">
+        <v>8.092939900000001</v>
+      </c>
+      <c r="Q100">
+        <v>16.4929399</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.050043317560571</v>
+      </c>
+      <c r="T100">
+        <v>50.91513295457348</v>
+      </c>
+      <c r="U100">
+        <v>0.055</v>
+      </c>
+      <c r="V100">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W100">
+        <v>0.04565</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>4.824532157664143</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.105683517451767</v>
+      </c>
+      <c r="C101">
+        <v>0.9048154752242041</v>
+      </c>
+      <c r="D101">
+        <v>26.2318154752242</v>
+      </c>
+      <c r="E101">
+        <v>39.027</v>
+      </c>
+      <c r="F101">
+        <v>46.827</v>
+      </c>
+      <c r="G101">
+        <v>21.5</v>
+      </c>
+      <c r="H101">
+        <v>39.5</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>20.7</v>
+      </c>
+      <c r="K101">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="L101">
+        <v>12.3</v>
+      </c>
+      <c r="M101">
+        <v>2.575485</v>
+      </c>
+      <c r="N101">
+        <v>9.724515</v>
+      </c>
+      <c r="O101">
+        <v>1.653167549999999</v>
+      </c>
+      <c r="P101">
+        <v>8.071347450000001</v>
+      </c>
+      <c r="Q101">
+        <v>16.47134745</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>6.049001745176691</v>
+      </c>
+      <c r="T101">
+        <v>101.6225487840623</v>
+      </c>
+      <c r="U101">
+        <v>0.055</v>
+      </c>
+      <c r="V101">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W101">
+        <v>0.04565</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>4.775799509606928</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
